--- a/tools/latest.xlsx
+++ b/tools/latest.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10911"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucifer/vscode_Luci_scripts/HBCD-DOCS/hbcd-docs-internal/tools/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CE57FA-1280-9A42-AC04-C5EE3F24F43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="🤩 public data release" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="🤩 public data release"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -289,6 +283,9 @@
     <t>C-PACEs</t>
   </si>
   <si>
+    <t>Summary scores for `sed_bm_paces` are currently calculated as the sum of individual item responses rather than the average. Until corrected, users may compute their own average-based summary scores using the item-level data provided in the dataset.</t>
+  </si>
+  <si>
     <t>[DATA ERROR] - 2 corrupt files in MRI raw BIDS (func)</t>
   </si>
   <si>
@@ -433,6 +430,9 @@
     <t>On hold- need more info</t>
   </si>
   <si>
+    <t>Instruction</t>
+  </si>
+  <si>
     <t>Instruction text in each form&amp;apos;s metadata is automatically extracted from the most recent `instruction` field in the REDCap Data Dictionary (based on field order). Because this process is automated, it may produce the following issues: (1) If an instruction spans multiple fields, only the last portion will be captured and/or (2) Some fields may display text intended for a previous section. Until this is corrected, please refer to original forms for accurate instruction text.</t>
   </si>
   <si>
@@ -451,6 +451,9 @@
     <t>MLDS</t>
   </si>
   <si>
+    <t>Total non-parental hours/week (`ncl_ch_mlds_arr_hr_wk`) includes implausible values due to data entry errors. Exclude values &gt;168 hours from analysis.</t>
+  </si>
+  <si>
     <t>[FUTURE DATA CORRECTION]- "does not apply" should = 8 for ECBQ</t>
   </si>
   <si>
@@ -550,6 +553,9 @@
     <t>EPDS</t>
   </si>
   <si>
+    <t xml:space="preserve"> Some V01-V03 records show inconsistencies between item responses and the calculated sum score, including (1) items present, but sum score is null; (2) items null, but sum score is 0.</t>
+  </si>
+  <si>
     <t>Anthro: ph_ch_anthro_head_for_age_boys_z_score</t>
   </si>
   <si>
@@ -562,6 +568,9 @@
     <t>APA 1/2</t>
   </si>
   <si>
+    <t>APA Level 2 was sometimes administered despite unmet gating criteria (e.g., missing Level 1 responses). These cases are not scored (“No additional inquiry required”) even when Level 2 responses are present. Level 2 item data will be removed to avoid confusion.</t>
+  </si>
+  <si>
     <t>[DD+DATA ERROR] Nail type field added for 2.0 all "Unknown"</t>
   </si>
   <si>
@@ -577,9 +586,15 @@
     <t>Healthv2 Preg</t>
   </si>
   <si>
+    <t>The field for the date when PNV was stopped (`pex_bm_healthv2_preg__exp__pnv_007__01`) is blank, despite participants having reported stopping.</t>
+  </si>
+  <si>
     <t>[LORIS TO REVIEW]- aspirin items in health v2 preg</t>
   </si>
   <si>
+    <t>Note that items about aspirin use (`pex_bm_healthv2_preg__exp__pnv_{011|012}`) are largely blank.</t>
+  </si>
+  <si>
     <t>[DATA REQUEST]- consistent ICD code names</t>
   </si>
   <si>
@@ -604,9 +619,15 @@
     <t>Data Type</t>
   </si>
   <si>
+    <t>Summary score variables in the Bayley and CDI are misclassified as text in the metadata, which may cause formatting issues in some tools.</t>
+  </si>
+  <si>
     <t>DD &amp;apos;instruction&amp;apos; field all blank</t>
   </si>
   <si>
+    <t>The &amp;apos;instruction&amp;apos; Data Dictionary element is currently blank.</t>
+  </si>
+  <si>
     <t>EEG file was not re-id&amp;apos;d (put in RTD) need to dig into how it happened -</t>
   </si>
   <si>
@@ -683,40 +704,14 @@
   </si>
   <si>
     <t>Tabulated XCP-D Myers-Labonte tables (`img_xcpd_hash-{X}_space-fsLR_seg-MyersLabonte_stat-mean_desc-_morph`) metadata will be corrected to have a `sub_domain` value of `Structural MRI` (currently `Resting State fMRI`).</t>
-  </si>
-  <si>
-    <t>Instruction</t>
-  </si>
-  <si>
-    <t>Summary score variables in the Bayley and CDI are misclassified as text in the metadata, which may cause formatting issues in some tools.</t>
-  </si>
-  <si>
-    <t>Total non-parental hours/week (`ncl_ch_mlds_arr_hr_wk`) includes implausible values due to data entry errors. Exclude values &gt;168 hours from analysis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Some V01-V03 records show inconsistencies between item responses and the calculated sum score, including (1) items present, but sum score is null; (2) items null, but sum score is 0.</t>
-  </si>
-  <si>
-    <t>The field for the date when PNV was stopped (`pex_bm_healthv2_preg__exp__pnv_007__01`) is blank, despite participants having reported stopping.</t>
-  </si>
-  <si>
-    <t>Note that items about aspirin use (`pex_bm_healthv2_preg__exp__pnv_{011|012}`) are largely blank.</t>
-  </si>
-  <si>
-    <t>Summary scores for `sed_bm_paces` are currently calculated as the sum of individual item responses rather than the average. Until corrected, users may compute their own average-based summary scores using the item-level data provided in the dataset.</t>
-  </si>
-  <si>
-    <t>APA Level 2 was sometimes administered despite unmet gating criteria (e.g., missing Level 1 responses). These cases are not scored (“No additional inquiry required”) even when Level 2 responses are present. Level 2 item data will be removed to avoid confusion.</t>
-  </si>
-  <si>
-    <t>The &amp;apos;instruction&amp;apos; Data Dictionary element is currently blank.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -739,13 +734,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFffffff"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -759,42 +748,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6D6D6"/>
+        <fgColor rgb="FFd6d6d6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4C4C4"/>
+        <fgColor rgb="FFc4c4c4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF007F"/>
+        <fgColor rgb="FFff007f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9D99B9"/>
+        <fgColor rgb="FF9d99b9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00C875"/>
+        <fgColor rgb="FF00c875"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF66CCFF"/>
+        <fgColor rgb="FF66ccff"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF007EB5"/>
+        <fgColor rgb="FF007eb5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDAB3D"/>
+        <fgColor rgb="FFfdab3d"/>
       </patternFill>
     </fill>
     <fill>
@@ -804,47 +793,47 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF2F4A"/>
+        <fgColor rgb="FFdf2f4a"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9D50DD"/>
+        <fgColor rgb="FF9d50dd"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF6D3B"/>
+        <fgColor rgb="FFff6d3b"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBB3354"/>
+        <fgColor rgb="FFbb3354"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCAB641"/>
+        <fgColor rgb="FFcab641"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9CD326"/>
+        <fgColor rgb="FF9cd326"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCB00"/>
+        <fgColor rgb="FFffcb00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF563E3E"/>
+        <fgColor rgb="FF563e3e"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF5AC4"/>
+        <fgColor rgb="FFff5ac4"/>
       </patternFill>
     </fill>
   </fills>
@@ -858,16 +847,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </left>
       <right style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </right>
       <top style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -882,101 +871,107 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="31">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="14" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="18" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="19" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -987,10 +982,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1028,71 +1023,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1120,7 +1115,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1143,11 +1138,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1156,13 +1151,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1172,7 +1167,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1181,7 +1176,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1190,7 +1185,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1198,10 +1193,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1266,22 +1261,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L70"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="255.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="28" width="40.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="29" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="30" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="28" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="28" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="28" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="28" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="28" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="28" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="28" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="28" width="255.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="28" width="20.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1319,7 +1320,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -1351,7 +1352,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
@@ -1379,7 +1380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
@@ -1411,7 +1412,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
         <v>31</v>
       </c>
@@ -1443,7 +1444,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -1475,12 +1476,16 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
+      <c r="B7" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="C7" s="6">
+        <v>21.1</v>
+      </c>
       <c r="D7" s="7"/>
       <c r="E7" s="8" t="s">
         <v>37</v>
@@ -1507,7 +1512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
         <v>46</v>
       </c>
@@ -1539,7 +1544,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
@@ -1571,7 +1576,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
         <v>52</v>
       </c>
@@ -1603,7 +1608,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
         <v>54</v>
       </c>
@@ -1639,7 +1644,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
         <v>56</v>
       </c>
@@ -1675,7 +1680,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>59</v>
       </c>
@@ -1711,7 +1716,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>62</v>
       </c>
@@ -1747,7 +1752,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>66</v>
       </c>
@@ -1783,7 +1788,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20">
       <c r="A16" s="4" t="s">
         <v>71</v>
       </c>
@@ -1819,7 +1824,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20">
       <c r="A17" s="4" t="s">
         <v>76</v>
       </c>
@@ -1853,7 +1858,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20">
       <c r="A18" s="4" t="s">
         <v>80</v>
       </c>
@@ -1887,7 +1892,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20">
       <c r="A19" s="4" t="s">
         <v>83</v>
       </c>
@@ -1921,7 +1926,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="20">
       <c r="A20" s="4" t="s">
         <v>87</v>
       </c>
@@ -1951,22 +1956,22 @@
         <v>88</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>227</v>
+        <v>89</v>
       </c>
       <c r="L20" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20">
       <c r="A21" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" s="20">
         <v>2.1</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>16</v>
@@ -1981,21 +1986,21 @@
         <v>33</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B22" s="20">
         <v>2.1</v>
@@ -2008,10 +2013,10 @@
         <v>67</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>15</v>
@@ -2020,18 +2025,18 @@
         <v>16</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L22" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20">
       <c r="A23" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B23" s="20">
         <v>2.1</v>
@@ -2056,18 +2061,18 @@
         <v>16</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L23" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="20">
         <v>2.1</v>
@@ -2090,18 +2095,18 @@
         <v>16</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L24" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20">
       <c r="A25" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="20">
         <v>2.1</v>
@@ -2129,15 +2134,15 @@
         <v>40</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L25" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="20">
         <v>2.1</v>
@@ -2165,15 +2170,15 @@
         <v>40</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L26" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20">
       <c r="A27" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="20">
         <v>2.1</v>
@@ -2198,18 +2203,18 @@
         <v>16</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L27" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="20">
@@ -2232,18 +2237,18 @@
         <v>16</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L28" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20">
       <c r="A29" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="20">
@@ -2266,18 +2271,18 @@
         <v>16</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L29" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="22">
         <v>3</v>
@@ -2300,18 +2305,18 @@
         <v>16</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L30" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20">
       <c r="A31" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="6"/>
@@ -2332,18 +2337,18 @@
         <v>16</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L31" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="20">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="22">
         <v>3</v>
@@ -2366,18 +2371,18 @@
         <v>16</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L32" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="20">
       <c r="A33" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="22">
         <v>3</v>
@@ -2400,18 +2405,18 @@
         <v>16</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L33" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="20">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="22">
         <v>3</v>
@@ -2434,18 +2439,18 @@
         <v>16</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L34" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="20">
       <c r="A35" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="6"/>
@@ -2466,18 +2471,18 @@
         <v>16</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L35" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="22">
         <v>3</v>
@@ -2497,21 +2502,21 @@
         <v>33</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L36" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="20">
       <c r="A37" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B37" s="22">
         <v>3</v>
@@ -2534,18 +2539,18 @@
         <v>16</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L37" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="20">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B38" s="22">
         <v>3</v>
@@ -2568,18 +2573,18 @@
         <v>16</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="K38" s="29" t="s">
-        <v>223</v>
+        <v>144</v>
+      </c>
+      <c r="K38" s="27" t="s">
+        <v>145</v>
       </c>
       <c r="L38" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="20">
       <c r="A39" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B39" s="22">
         <v>3</v>
@@ -2602,18 +2607,18 @@
         <v>16</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L39" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="20">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B40" s="22">
         <v>3</v>
@@ -2636,18 +2641,18 @@
         <v>16</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L40" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="20">
       <c r="A41" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B41" s="22">
         <v>3</v>
@@ -2673,15 +2678,15 @@
         <v>50</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L41" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="20">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B42" s="22">
         <v>3</v>
@@ -2704,18 +2709,18 @@
         <v>16</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="L42" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="20">
       <c r="A43" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B43" s="22">
         <v>3</v>
@@ -2738,18 +2743,18 @@
         <v>16</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L43" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="20">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B44" s="22">
         <v>3</v>
@@ -2775,15 +2780,15 @@
         <v>50</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L44" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="20">
       <c r="A45" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -2792,7 +2797,7 @@
         <v>13</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>14</v>
@@ -2804,18 +2809,18 @@
         <v>16</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L45" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="20">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B46" s="22">
         <v>3</v>
@@ -2823,7 +2828,7 @@
       <c r="C46" s="6"/>
       <c r="D46" s="7"/>
       <c r="E46" s="17" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F46" s="24" t="s">
         <v>68</v>
@@ -2832,22 +2837,22 @@
         <v>68</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I46" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="16" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="20">
       <c r="A47" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B47" s="22">
         <v>3</v>
@@ -2870,18 +2875,18 @@
         <v>16</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L47" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="20">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B48" s="22">
         <v>3</v>
@@ -2904,18 +2909,18 @@
         <v>16</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L48" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="20">
       <c r="A49" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B49" s="22">
         <v>3</v>
@@ -2938,18 +2943,18 @@
         <v>16</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="K49" t="s">
-        <v>224</v>
+        <v>178</v>
+      </c>
+      <c r="K49" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="L49" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="20">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B50" s="22">
         <v>3</v>
@@ -2975,15 +2980,15 @@
         <v>50</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="L50" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="20">
       <c r="A51" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B51" s="22">
         <v>3</v>
@@ -3006,24 +3011,24 @@
         <v>16</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="L51" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="20">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="6"/>
       <c r="D52" s="7"/>
       <c r="E52" s="25" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F52" s="24" t="s">
         <v>68</v>
@@ -3041,15 +3046,15 @@
         <v>81</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="L52" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="20">
       <c r="A53" s="4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="6"/>
@@ -3070,18 +3075,18 @@
         <v>16</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="L53" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="20">
       <c r="A54" s="4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -3102,18 +3107,18 @@
         <v>16</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="L54" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="20">
       <c r="A55" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B55" s="22">
         <v>3</v>
@@ -3136,18 +3141,18 @@
         <v>16</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="L55" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="20">
       <c r="A56" s="4" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B56" s="22">
         <v>3</v>
@@ -3177,9 +3182,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="20">
       <c r="A57" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B57" s="22">
         <v>3</v>
@@ -3207,9 +3212,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="20">
       <c r="A58" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B58" s="22">
         <v>3</v>
@@ -3217,7 +3222,7 @@
       <c r="C58" s="6"/>
       <c r="D58" s="7"/>
       <c r="E58" s="15" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F58" s="25" t="s">
         <v>77</v>
@@ -3232,18 +3237,18 @@
         <v>16</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="K58" t="s">
-        <v>222</v>
+        <v>200</v>
+      </c>
+      <c r="K58" s="27" t="s">
+        <v>201</v>
       </c>
       <c r="L58" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="20">
       <c r="A59" s="4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B59" s="22">
         <v>3</v>
@@ -3266,18 +3271,18 @@
         <v>16</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="L59" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="20">
       <c r="A60" s="4" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B60" s="20">
         <v>2.1</v>
@@ -3286,7 +3291,7 @@
         <v>21.1</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>16</v>
@@ -3301,21 +3306,21 @@
         <v>33</v>
       </c>
       <c r="I60" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="L60" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="20">
       <c r="A61" s="4" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B61" s="20">
         <v>2.1</v>
@@ -3324,7 +3329,7 @@
         <v>21</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>16</v>
@@ -3339,21 +3344,21 @@
         <v>15</v>
       </c>
       <c r="I61" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="L61" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="20">
       <c r="A62" s="4" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B62" s="20">
         <v>2.1</v>
@@ -3362,7 +3367,7 @@
         <v>21</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>16</v>
@@ -3377,21 +3382,21 @@
         <v>33</v>
       </c>
       <c r="I62" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="L62" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="20">
       <c r="A63" s="4" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B63" s="20">
         <v>2.1</v>
@@ -3400,7 +3405,7 @@
         <v>21</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>16</v>
@@ -3415,21 +3420,21 @@
         <v>33</v>
       </c>
       <c r="I63" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>40</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="L63" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="20">
       <c r="A64" s="4" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B64" s="20">
         <v>2.1</v>
@@ -3438,7 +3443,7 @@
         <v>21</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>16</v>
@@ -3453,21 +3458,21 @@
         <v>33</v>
       </c>
       <c r="I64" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="L64" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="20">
       <c r="A65" s="4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B65" s="20">
         <v>2.1</v>
@@ -3476,7 +3481,7 @@
         <v>21</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>16</v>
@@ -3491,21 +3496,21 @@
         <v>15</v>
       </c>
       <c r="I65" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="L65" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="20">
       <c r="A66" s="4" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B66" s="20">
         <v>2.1</v>
@@ -3514,7 +3519,7 @@
         <v>21</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>16</v>
@@ -3529,21 +3534,21 @@
         <v>15</v>
       </c>
       <c r="I66" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>44</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="L66" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="20">
       <c r="A67" s="4" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B67" s="20">
         <v>2.1</v>
@@ -3552,7 +3557,7 @@
         <v>21</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>16</v>
@@ -3567,21 +3572,21 @@
         <v>15</v>
       </c>
       <c r="I67" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="L67" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="20">
       <c r="A68" s="4" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B68" s="20">
         <v>2.1</v>
@@ -3590,7 +3595,7 @@
         <v>21</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>16</v>
@@ -3605,21 +3610,21 @@
         <v>33</v>
       </c>
       <c r="I68" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="L68" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="20">
       <c r="A69" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B69" s="20">
         <v>2.1</v>
@@ -3628,7 +3633,7 @@
         <v>21</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>16</v>
@@ -3643,21 +3648,31 @@
         <v>33</v>
       </c>
       <c r="I69" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="L69" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="20">
+      <c r="A70" s="27"/>
       <c r="B70" s="5"/>
       <c r="C70" s="6"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="27"/>
+      <c r="J70" s="27"/>
+      <c r="K70" s="27"/>
+      <c r="L70" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/latest.xlsx
+++ b/tools/latest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10911"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8A50E8-FE8D-D149-A15C-291DC826C540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1257911-F396-D444-BC29-EA8C7D692EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -662,9 +662,6 @@
     <t>Scanner Info</t>
   </si>
   <si>
-    <t>Scanner information (currently available in the scans TSV files within the raw BIDS data as well as all sidecar JSON files) will be provided as tabulated data.</t>
-  </si>
-  <si>
     <t>RTDs ONLY - IGNORE</t>
   </si>
   <si>
@@ -795,13 +792,92 @@
   </si>
   <si>
     <t>Addition of creatinine results (`bio_creat_u`).</t>
+  </si>
+  <si>
+    <r>
+      <t>Scanner information must currently be parsed from raw BIDS data (specifically the scans .tsv files), as described [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>here</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>](</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://docs.hbcdstudy.org/latest/help/faq/#faq-scanner-info</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>). Future releases will include a dedicated 'MRI Info' table that summarizes scanner information across participants, similar to the ABCD study ([</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>see details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>](</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://docs.abcdstudy.org/latest/documentation/imaging/admin.html#mr_y_adm__info</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>)).</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,6 +894,25 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFCE9178"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Menlo"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="21">
@@ -935,7 +1030,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1000,6 +1095,7 @@
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2518,7 +2614,7 @@
         <v>123</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>20</v>
@@ -3809,8 +3905,8 @@
       <c r="J65" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="K65" s="7" t="s">
-        <v>215</v>
+      <c r="K65" s="22" t="s">
+        <v>259</v>
       </c>
       <c r="L65" s="6" t="s">
         <v>20</v>
@@ -3818,7 +3914,7 @@
     </row>
     <row r="66" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" s="7">
         <v>3</v>
@@ -3830,7 +3926,7 @@
         <v>13</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>39</v>
@@ -3839,7 +3935,7 @@
         <v>39</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>17</v>
@@ -3848,7 +3944,7 @@
         <v>41</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L66" s="6" t="s">
         <v>20</v>
@@ -3856,7 +3952,7 @@
     </row>
     <row r="67" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B67" s="7">
         <v>3</v>
@@ -3883,10 +3979,10 @@
         <v>17</v>
       </c>
       <c r="J67" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="K67" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="K67" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="L67" s="6" t="s">
         <v>20</v>
@@ -3894,7 +3990,7 @@
     </row>
     <row r="68" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -3932,7 +4028,7 @@
     </row>
     <row r="69" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -3959,10 +4055,10 @@
         <v>17</v>
       </c>
       <c r="J69" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="K69" s="7" t="s">
         <v>225</v>
-      </c>
-      <c r="K69" s="7" t="s">
-        <v>226</v>
       </c>
       <c r="L69" s="6" t="s">
         <v>20</v>
@@ -3970,7 +4066,7 @@
     </row>
     <row r="70" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -3997,10 +4093,10 @@
         <v>17</v>
       </c>
       <c r="J70" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="K70" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="K70" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="L70" s="6" t="s">
         <v>20</v>
@@ -4008,7 +4104,7 @@
     </row>
     <row r="71" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B71" s="7">
         <v>2.1</v>
@@ -4035,10 +4131,10 @@
         <v>85</v>
       </c>
       <c r="J71" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="K71" s="7" t="s">
         <v>231</v>
-      </c>
-      <c r="K71" s="7" t="s">
-        <v>232</v>
       </c>
       <c r="L71" s="6" t="s">
         <v>20</v>
@@ -4046,7 +4142,7 @@
     </row>
     <row r="72" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B72" s="7">
         <v>2.1</v>
@@ -4073,10 +4169,10 @@
         <v>85</v>
       </c>
       <c r="J72" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="K72" s="7" t="s">
         <v>234</v>
-      </c>
-      <c r="K72" s="7" t="s">
-        <v>235</v>
       </c>
       <c r="L72" s="6" t="s">
         <v>20</v>
@@ -4084,7 +4180,7 @@
     </row>
     <row r="73" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B73" s="7">
         <v>2.1</v>
@@ -4111,10 +4207,10 @@
         <v>85</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L73" s="6" t="s">
         <v>20</v>
@@ -4122,7 +4218,7 @@
     </row>
     <row r="74" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B74" s="7">
         <v>2.1</v>
@@ -4152,7 +4248,7 @@
         <v>115</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L74" s="6" t="s">
         <v>20</v>
@@ -4160,7 +4256,7 @@
     </row>
     <row r="75" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B75" s="7">
         <v>2.1</v>
@@ -4187,10 +4283,10 @@
         <v>85</v>
       </c>
       <c r="J75" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="K75" s="7" t="s">
         <v>241</v>
-      </c>
-      <c r="K75" s="7" t="s">
-        <v>242</v>
       </c>
       <c r="L75" s="6" t="s">
         <v>20</v>
@@ -4198,7 +4294,7 @@
     </row>
     <row r="76" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B76" s="7">
         <v>2.1</v>
@@ -4225,10 +4321,10 @@
         <v>85</v>
       </c>
       <c r="J76" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="K76" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="K76" s="7" t="s">
-        <v>245</v>
       </c>
       <c r="L76" s="6" t="s">
         <v>20</v>
@@ -4236,7 +4332,7 @@
     </row>
     <row r="77" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B77" s="7">
         <v>2.1</v>
@@ -4266,7 +4362,7 @@
         <v>41</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L77" s="6" t="s">
         <v>20</v>
@@ -4274,7 +4370,7 @@
     </row>
     <row r="78" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B78" s="7">
         <v>2.1</v>
@@ -4301,10 +4397,10 @@
         <v>85</v>
       </c>
       <c r="J78" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="K78" s="7" t="s">
         <v>249</v>
-      </c>
-      <c r="K78" s="7" t="s">
-        <v>250</v>
       </c>
       <c r="L78" s="6" t="s">
         <v>20</v>
@@ -4312,7 +4408,7 @@
     </row>
     <row r="79" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B79" s="7">
         <v>2.1</v>
@@ -4339,10 +4435,10 @@
         <v>85</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L79" s="6" t="s">
         <v>20</v>
@@ -4350,7 +4446,7 @@
     </row>
     <row r="80" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B80" s="7">
         <v>2.1</v>
@@ -4377,10 +4473,10 @@
         <v>85</v>
       </c>
       <c r="J80" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="K80" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="K80" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="L80" s="6" t="s">
         <v>20</v>
@@ -4388,7 +4484,7 @@
     </row>
     <row r="81" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B81" s="7">
         <v>2.1</v>
@@ -4415,10 +4511,10 @@
         <v>85</v>
       </c>
       <c r="J81" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="K81" s="7" t="s">
         <v>257</v>
-      </c>
-      <c r="K81" s="7" t="s">
-        <v>258</v>
       </c>
       <c r="L81" s="6" t="s">
         <v>20</v>

--- a/tools/latest.xlsx
+++ b/tools/latest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10911"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1257911-F396-D444-BC29-EA8C7D692EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50922CF-CA13-034A-9820-60114A61D451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🤩 public data release" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="254">
   <si>
     <t>Name</t>
   </si>
@@ -143,7 +143,7 @@
     <t>ERICA</t>
   </si>
   <si>
-    <t>Remove 2 data points specified by WG from the ERICA Codes (3-9M) table.</t>
+    <t>Per WG, remove 2 data points from the ERICA Codes (3-9M) *[BR data only]*.</t>
   </si>
   <si>
     <t>[DATA ERROR]- negative adjusted age</t>
@@ -164,7 +164,7 @@
     <t>br_pending</t>
   </si>
   <si>
-    <t>Recalculate all `age` and `date_taken` fields using *visit date* instead of *date coded*; currently to be excluded from PR2.1.</t>
+    <t>Recalculate all `age` &amp; `date_taken` fields using *visit date* instead of *date coded*; currently to be excluded from PR2.1.</t>
   </si>
   <si>
     <t>[POSSIBLE DATA ERROR]- relationship status at V03</t>
@@ -185,7 +185,7 @@
     <t>FAD</t>
   </si>
   <si>
-    <t>Incorrect scoring for N=4 V06 participants: Summary scores incorrectly set to `0` with &lt;3 item responses (should be missing)</t>
+    <t>N=4 V06 participants with &lt;3 item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
   </si>
   <si>
     <t>[DATA REQUEST]- add back in missing employment variables</t>
@@ -194,13 +194,10 @@
     <t>SOCIAL &amp; ENVIRONMENTAL DETERMINANTS</t>
   </si>
   <si>
-    <t>Not done</t>
-  </si>
-  <si>
-    <t>sed_bm_demo</t>
-  </si>
-  <si>
-    <t>Addition of following variables: `work_002_post` (Worked for pay while pregnant), `work_003_post` (Job held for 20+ hours while pregnant), `work_004_post` (Worked 35+ hours while pregnant), `work_004__01` (Job held for 1 month since first study visit).</t>
+    <t>Demo</t>
+  </si>
+  <si>
+    <t>Add `work_{002–004}_post` (worked for pay/≥20/≥35 hours while pregnant) and `work_004__01` (job held ≥1 month since V01) (adult table).</t>
   </si>
   <si>
     <t>[IMAGING] Cook's distance for imaging</t>
@@ -209,342 +206,333 @@
     <t>[DATA ERROR]- ecPROMIS child-caregiver infant</t>
   </si>
   <si>
-    <t>ecPROMIS Ch-CG Int (Inf)</t>
-  </si>
-  <si>
-    <t>Incorrect scoring for N=12 V03 participants in `mh_cg_pms__cc__inf`: Summary scores incorrectly set to `0` with &lt;3 item responses (should be missing)</t>
-  </si>
-  <si>
-    <t>[SCORING NEEDED]- MAPS EASI at v07</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- add cook's distance to tabulated imaging data</t>
+    <t>ecPROMIS CC</t>
+  </si>
+  <si>
+    <t>N=12 V03 participants with &lt;3 item responses are incorrectly scored as `0` in `mh_cg_pms__cc__inf`; set values to null prior to analysis.</t>
+  </si>
+  <si>
+    <t>Anthro: LT goal for implementing score calculation in ETL based on EDD</t>
+  </si>
+  <si>
+    <t>Add age-based z-scores to `ph_ch_anthro` (see [Z-Scores Excluded](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]- add in LORIS imaging form variables</t>
+  </si>
+  <si>
+    <t>Dev Done</t>
+  </si>
+  <si>
+    <t>Summary Forms</t>
+  </si>
+  <si>
+    <t>Add MRI 'Scan Session' and 'Data' Summary Forms to release data with information from the MRI technician obtained on day of scan.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- age fields in EEG data</t>
+  </si>
+  <si>
+    <t>EEG</t>
+  </si>
+  <si>
+    <t>Age fields</t>
+  </si>
+  <si>
+    <t>Chronological and adjusted age fall outside of 3-9 months in N=74 V03 sessions due to site entry errors; exclude age values prior to analysis.</t>
+  </si>
+  <si>
+    <t>Genomics - OLINK data proteomics</t>
+  </si>
+  <si>
+    <t>21.0</t>
+  </si>
+  <si>
+    <t>BIOSPECIMEN &amp; OMICS</t>
+  </si>
+  <si>
+    <t>Archived to BR</t>
+  </si>
+  <si>
+    <t>Olink</t>
+  </si>
+  <si>
+    <t>Add Olink Explore 384 Inflammation 1 Panel, proteomics measure of maternal inflammation during pregnancy</t>
+  </si>
+  <si>
+    <t>TLFB PNR; wrong weeks reported comparison</t>
+  </si>
+  <si>
+    <t>Ongoing</t>
+  </si>
+  <si>
+    <t>PREGNANCY &amp; EXPOSURE</t>
+  </si>
+  <si>
+    <t>TLFB</t>
+  </si>
+  <si>
+    <t>PNR data were incorrectly reported using TLFB versions 1/2 and will be updated to [version 3 specific to PNR](https://docs.hbcdstudy.org/latest/instruments/pregexp/su/tlfb/#v3).</t>
+  </si>
+  <si>
+    <t>Bayley item-level scores</t>
+  </si>
+  <si>
+    <t>NEUROCOGNITION &amp; LANGUAGE</t>
+  </si>
+  <si>
+    <t>Bayley-4</t>
+  </si>
+  <si>
+    <t>Add item-level scores.</t>
+  </si>
+  <si>
+    <t>Inclusion or Exclusion of language fields across instruments</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Add language of administration across all instruments where applicable.</t>
+  </si>
+  <si>
+    <t>add unit for nails_results_nail_weight variable</t>
+  </si>
+  <si>
+    <t>Nails</t>
+  </si>
+  <si>
+    <t>Add unit (mg) for `nails_results_nail_weight` variable.</t>
+  </si>
+  <si>
+    <t>All decline to answer will still report as zero - eHITS</t>
+  </si>
+  <si>
+    <t>SED</t>
+  </si>
+  <si>
+    <t>eHITS</t>
+  </si>
+  <si>
+    <t>Participants missing all item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
+  </si>
+  <si>
+    <t>[SCORING CORRECTION NEEDED]- current PACEs</t>
+  </si>
+  <si>
+    <t>C-PACEs</t>
+  </si>
+  <si>
+    <t>Summary scores are inaccurate; until corrected, users can compute scores following the provided scoring documentation.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- Study Navigator blank checkboxes</t>
+  </si>
+  <si>
+    <t>Study Navigators</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE</t>
+  </si>
+  <si>
+    <t>Populate SUBSTANCE_USE and OTHER checkbox fields.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- missing participants from tabulated EEG data</t>
+  </si>
+  <si>
+    <t>MADE</t>
+  </si>
+  <si>
+    <t>N=3 V04 session derivatives are missing corresponding tabulated data for FACE/MMN tasks. See [HBCD Private Release Notes](https://hbcd-docs-private.lassoinformatics.com/#download) for impacted participant IDs.</t>
+  </si>
+  <si>
+    <t>[MISSING VARIABLE]- sed_bm_demo_income_002</t>
+  </si>
+  <si>
+    <t>Add V01 household income (`income_002`) (adult table).</t>
+  </si>
+  <si>
+    <t>[MISSING VARIABLES]- dems other bio parent</t>
+  </si>
+  <si>
+    <t>Add variables on Other Biological Parent (adult table).</t>
+  </si>
+  <si>
+    <t>Visit info SU flags: add rolled up Stimulant flag</t>
+  </si>
+  <si>
+    <t>SU Flags</t>
+  </si>
+  <si>
+    <t>A derived/rolled up substance use flag for Stimulants will be added based on positive instrument-specific Stimulant results.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- including creatinine field</t>
+  </si>
+  <si>
+    <t>Urine</t>
+  </si>
+  <si>
+    <t>Add creatinine results (`bio_creat_u`).</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]- add nails tox results to par_visit_data substance use flags</t>
+  </si>
+  <si>
+    <t>Visit Info</t>
+  </si>
+  <si>
+    <t>SU flags will include Nail toxicology results in addition to Urine.</t>
+  </si>
+  <si>
+    <t>remove descriptive fields that were accidentally included</t>
+  </si>
+  <si>
+    <t>Remove descriptive fields (e.g. `roster_001__00`) *[BR data only]*.</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]-remove a few ERICA fields from data release</t>
+  </si>
+  <si>
+    <t>Remove date taken, age, and language fields (computed based on *date coded*) to exclude from patch 2.1 *[BR data only]*.</t>
+  </si>
+  <si>
+    <t>[REMOVE VARIABLE]- ph_ch_anthro_002</t>
+  </si>
+  <si>
+    <t>Remove `ph_ch_anthro_002`.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- PA/greenspace type_Data= text so breaking lasso dashboard</t>
+  </si>
+  <si>
+    <t>ecPROMIS-PAG</t>
+  </si>
+  <si>
+    <t>Add scores to `ph_cg_pms__pags`. Until added, scores can be calculated by following the [Scoring Procedures](https://docs.hbcdstudy.org/latest/instruments/physhealth/ecpromis-pags/#scoring) documentation.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- implausible gestational ages in multiple instruments</t>
+  </si>
+  <si>
+    <t>Started, outprioritized</t>
+  </si>
+  <si>
+    <t>Implausible GA</t>
+  </si>
+  <si>
+    <t>A small subset of participants have implausible `gestational_age` (V01 only) values  for one or more instrument. Until corrected, review GA distribution to exclude outliers from analysis (should be positive and generally &lt; 45 weeks).</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- missing sleep score fields- ecPROMIS SLEEP</t>
+  </si>
+  <si>
+    <t>ecPROMIS- Sleep</t>
+  </si>
+  <si>
+    <t>Add `ph_cg_pms__sleep`  summary scores</t>
+  </si>
+  <si>
+    <t>Visit info: inaccurate missed_date values (removed from 2.0 release for now)</t>
+  </si>
+  <si>
+    <t>Date of missed visit (`visit_missed_date`) is currently excluded from the release due to inaccuracies and will be added once corrected.</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]- revise formatting of vision screener files</t>
+  </si>
+  <si>
+    <t>Vision Screener</t>
+  </si>
+  <si>
+    <t>Add more fields to `ph_ch_vs` (current release only includes completion status and overall screening results).</t>
+  </si>
+  <si>
+    <t>Instruction metadata extraction from REDCap DD</t>
+  </si>
+  <si>
+    <t>On hold- need more info</t>
+  </si>
+  <si>
+    <t>Instruction</t>
+  </si>
+  <si>
+    <t>Instruction text in each form's metadata is automatically extracted from the most recent `instruction` field in the REDCap Data Dictionary (based on field order). Because this process is automated, it may produce the following issues: (1) If an instruction spans multiple fields, only the last portion will be captured and/or (2) Some fields may display text intended for a previous section. Until this is corrected, please refer to original forms for accurate instruction text.</t>
+  </si>
+  <si>
+    <t>BIDs run label not in chronological order</t>
+  </si>
+  <si>
+    <t>Run ID</t>
+  </si>
+  <si>
+    <t>The `run-{X}` field may not reflect chronological acquisition order. While this affects both **raw BIDS and derivatives**, data remain internally consistent (i.e. run IDs match between raw and processed datasets).</t>
+  </si>
+  <si>
+    <t>[FUTURE DATA CORRECTION]- "does not apply" should = 8 for ECBQ</t>
+  </si>
+  <si>
+    <t>ECBQ</t>
+  </si>
+  <si>
+    <t>Change coding for "Does not apply" to 8 to match the IBQ-R.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- missing CDI fields + incorrectly set type_data</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>Set percentile scores in `ncl_ch_cdiwgen` (with the exception of `percentile_both`) to data type=integer.</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]- calculate SGA (intergrowth curves, anthro) LT solution into DB</t>
+  </si>
+  <si>
+    <t>Add sex-specific birth weight to `ph_ch_anthro` (see [Sex-Specific Birthweight for GA](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
+  </si>
+  <si>
+    <t>[FIELD UPDATE]- MAPSTL notes appear in score field</t>
+  </si>
+  <si>
+    <t>MAPS-TL</t>
+  </si>
+  <si>
+    <t>Notes appear in the score field in both versions (Infant/Toddlerhood) and will be moved to a separate field.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- MAPTSTL scores incorrectly marked as "not enough answers to compute score"</t>
+  </si>
+  <si>
+    <t>MAPS-TL (Tod)</t>
+  </si>
+  <si>
+    <t>Pro-rated scoring for `mh_cg_mapdb__tod` not yet implemented; N=16 participants missing scores.</t>
+  </si>
+  <si>
+    <t>[TYPE_DATA INCORRECT] - ph_ch_anthro_average_bmi</t>
+  </si>
+  <si>
+    <t>The Data Dictionary element `type_data` for `average_bmi` will be corrected to `double` (currently=`character`).</t>
+  </si>
+  <si>
+    <t>Add DICOMs to release</t>
+  </si>
+  <si>
+    <t>Source DICOMs</t>
+  </si>
+  <si>
+    <t>Add source DICOMs for all imaging modalities.</t>
+  </si>
+  <si>
+    <t>Add in 'ANALYSIS DATE' for biospecimens</t>
   </si>
   <si>
     <t>Blocked without leadership direction</t>
   </si>
   <si>
-    <t>Anthro: LT goal for implementing score calculation in ETL based on EDD</t>
-  </si>
-  <si>
-    <t>Addition of age-based z-scores to `ph_ch_anthro` (see [Z-Scores Excluded](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- add in LORIS imaging form variables</t>
-  </si>
-  <si>
-    <t>Dev Done</t>
-  </si>
-  <si>
-    <t>Summary Forms</t>
-  </si>
-  <si>
-    <t>Addition of MRI 'Scan Session' and 'Data' Summary Forms to release data with information from the MRI technician obtained on day of scan.</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- language of administration variable</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Addition of language of administration across all instruments where applicable.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- age fields in EEG data</t>
-  </si>
-  <si>
-    <t>EEG</t>
-  </si>
-  <si>
-    <t>Age fields</t>
-  </si>
-  <si>
-    <t>For N=74 V03 sessions, chronological and adjusted age fall outside 3–9 months due to site entry errors. Exclude out-of-range values for analysis.</t>
-  </si>
-  <si>
-    <t>Genomics - OLINK data proteomics</t>
-  </si>
-  <si>
-    <t>21.0</t>
-  </si>
-  <si>
-    <t>BIOSPECIMEN &amp; OMICS</t>
-  </si>
-  <si>
-    <t>Archived to BR</t>
-  </si>
-  <si>
-    <t>Olink</t>
-  </si>
-  <si>
-    <t>Addition of Olink Explore 384 Inflammation 1 Panel, proteomics measure of maternal inflammation during pregnancy</t>
-  </si>
-  <si>
-    <t>TLFB PNR; wrong weeks reported comparison</t>
-  </si>
-  <si>
-    <t>Ongoing</t>
-  </si>
-  <si>
-    <t>PREGNANCY &amp; EXPOSURE</t>
-  </si>
-  <si>
-    <t>TLFB</t>
-  </si>
-  <si>
-    <t>Weeks for postnatal recruits were mistakenly reported in the TLFB **versions 1** or **2** instead of [**version 3** adapted for PNR](https://docs.hbcdstudy.org/latest/instruments/pregexp/su/tlfb/#v3). These will be adjusted to **version 3**.</t>
-  </si>
-  <si>
-    <t>Bayley item-level scores</t>
-  </si>
-  <si>
-    <t>NEUROCOGNITION &amp; LANGUAGE</t>
-  </si>
-  <si>
-    <t>Bayley-4</t>
-  </si>
-  <si>
-    <t>Addition of item-level scores.</t>
-  </si>
-  <si>
-    <t>add unit for nails_results_nail_weight variable</t>
-  </si>
-  <si>
-    <t>Nails</t>
-  </si>
-  <si>
-    <t>Add unit (mg) for `nails_results_nail_weight` variable.</t>
-  </si>
-  <si>
-    <t>All decline to answer will still report as zero - eHITS</t>
-  </si>
-  <si>
-    <t>SED</t>
-  </si>
-  <si>
-    <t>eHITS</t>
-  </si>
-  <si>
-    <t>In `sed_bm_ehits`, participants with no responses are assigned a score of 0 instead of missing; convert to null before analysis.</t>
-  </si>
-  <si>
-    <t>[SCORING CORRECTION NEEDED]- current PACEs</t>
-  </si>
-  <si>
-    <t>C-PACEs</t>
-  </si>
-  <si>
-    <t>Summary scores for `sed_bm_paces` are currently calculated as the sum of individual item responses rather than the average. Until corrected, users may compute their own average-based summary scores using the item-level data provided in the dataset.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- Study Navigator blank checkboxes</t>
-  </si>
-  <si>
-    <t>Study Navigators</t>
-  </si>
-  <si>
-    <t>ADMINISTRATIVE</t>
-  </si>
-  <si>
-    <t>Populate SUBSTANCE_USE and OTHER checkbox fields.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- missing participants from tabulated EEG data</t>
-  </si>
-  <si>
-    <t>HBCD-MADE</t>
-  </si>
-  <si>
-    <t>N=3 V04 sessions in the HBCD-MADE derivatives for FACE and MMN tasks are missing corresponding tabulated data. File-based data should therefore be used for analyses. Impacted participant IDs are available via the [HBCD Private Release Notes](https://hbcd-docs-private.lassoinformatics.com/#download).</t>
-  </si>
-  <si>
-    <t>[MISSING VARIABLE]- sed_bm_demo_income_002</t>
-  </si>
-  <si>
-    <t>Demographics</t>
-  </si>
-  <si>
-    <t>V01 household income (`sed_bm_demo_income_002`) missing from adult demographics.</t>
-  </si>
-  <si>
-    <t>[MISSING VARIABLES]- dems other bio parent</t>
-  </si>
-  <si>
-    <t>Variables on the Other Biological Parent are missing from `sed_bm_demo`.</t>
-  </si>
-  <si>
-    <t>Visit info SU flags: add rolled up Stimulant flag</t>
-  </si>
-  <si>
-    <t>SU Flags</t>
-  </si>
-  <si>
-    <t>A derived/rolled up substance use flag for Stimulants will be added based on positive instrument-specific Stimulant results.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- including creatinine field</t>
-  </si>
-  <si>
-    <t>Urine</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- add nails tox results to par_visit_data substance use flags</t>
-  </si>
-  <si>
-    <t>VIsit Info</t>
-  </si>
-  <si>
-    <t>SU flags will include Nail toxicology results in addition to Urine.</t>
-  </si>
-  <si>
-    <t>remove descriptive fields that were accidentally included</t>
-  </si>
-  <si>
-    <t>Remove erroneously included descriptive fields (e.g. `sed_bm_demo_roster_001__00`).</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]-remove a few ERICA fields from data release</t>
-  </si>
-  <si>
-    <t>Remove ERICA variables specified by WG that are normally consortium-wide standard to include (data taken, age fields, and language).</t>
-  </si>
-  <si>
-    <t>[REMOVE VARIABLE]- ph_ch_anthro_002</t>
-  </si>
-  <si>
-    <t>Remove `ph_ch_anthro_002`.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- PA/greenspace type_Data= text so breaking lasso dashboard</t>
-  </si>
-  <si>
-    <t>ecPROMIS-PAG</t>
-  </si>
-  <si>
-    <t>Addition of summary scores to `ph_cg_pms__pags`. Until added, scores can be calculated by following the [Scoring Procedures](https://docs.hbcdstudy.org/latest/instruments/physhealth/ecpromis-pags/#scoring) documentation.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- implausible gestational ages in multiple instruments</t>
-  </si>
-  <si>
-    <t>Started, outprioritized</t>
-  </si>
-  <si>
-    <t>Implausible GA</t>
-  </si>
-  <si>
-    <t>A small subset of participants have implausible `gestational_age` (V01 only) values  for one or more instrument. Until corrected, review GA distribution to exclude outliers from analysis (should be positive and generally &lt; 45 weeks).</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- missing sleep score fields- ecPROMIS SLEEP</t>
-  </si>
-  <si>
-    <t>ecPROMIS- Sleep</t>
-  </si>
-  <si>
-    <t>Addition of summary scores to `ph_cg_pms__sleep`.</t>
-  </si>
-  <si>
-    <t>Visit info: inaccurate missed_date values (removed from 2.0 release for now)</t>
-  </si>
-  <si>
-    <t>Visit Level Data</t>
-  </si>
-  <si>
-    <t>Date of missed visit (`visit_missed_date`) is currently excluded from the release due to inaccuracies and will be added once corrected.</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- revise formatting of vision screener files</t>
-  </si>
-  <si>
-    <t>Vision Screener</t>
-  </si>
-  <si>
-    <t>Addition of more fields to `ph_ch_vs` (current release only includes completion status and overall screening results).</t>
-  </si>
-  <si>
-    <t>Instruction metadata extraction from REDCap DD</t>
-  </si>
-  <si>
-    <t>On hold- need more info</t>
-  </si>
-  <si>
-    <t>Instruction</t>
-  </si>
-  <si>
-    <t>Instruction text in each form's metadata is automatically extracted from the most recent `instruction` field in the REDCap Data Dictionary (based on field order). Because this process is automated, it may produce the following issues: (1) If an instruction spans multiple fields, only the last portion will be captured and/or (2) Some fields may display text intended for a previous section. Until this is corrected, please refer to original forms for accurate instruction text.</t>
-  </si>
-  <si>
-    <t>BIDs run label not in chronological order</t>
-  </si>
-  <si>
-    <t>Run ID</t>
-  </si>
-  <si>
-    <t>The `run-{X}` field may not reflect chronological acquisition order. While this affects both **raw BIDS and derivatives**, data remain internally consistent (i.e. run IDs match between raw and processed datasets).</t>
-  </si>
-  <si>
-    <t>[FUTURE DATA CORRECTION]- "does not apply" should = 8 for ECBQ</t>
-  </si>
-  <si>
-    <t>ECBQ</t>
-  </si>
-  <si>
-    <t>Change coding for "Does not apply" to 8 to match the IBQ-R.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- missing CDI fields + incorrectly set type_data</t>
-  </si>
-  <si>
-    <t>CDI</t>
-  </si>
-  <si>
-    <t>Set percentile scores in `ncl_ch_cdiwgen` (with the exception of `percentile_both`) to data type=integer.</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- calculate SGA (intergrowth curves, anthro) LT solution into DB</t>
-  </si>
-  <si>
-    <t>Addition of sex-specific birth weight to `ph_ch_anthro` (see [Sex-Specific Birthweight for GA](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
-  </si>
-  <si>
-    <t>[FIELD UPDATE]- MAPSTL notes appear in score field</t>
-  </si>
-  <si>
-    <t>MAPS-TL</t>
-  </si>
-  <si>
-    <t>Notes appear in the score field in both versions (Infant/Toddlerhood) and will be moved to a separate field.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- MAPTSTL scores incorrectly marked as "not enough answers to compute score"</t>
-  </si>
-  <si>
-    <t>MAPS-TL (Tod)</t>
-  </si>
-  <si>
-    <t>Pro-rated scoring is not yet applied for missing responses in the `mh_cg_mapdb__tod`, resulting in N=16 participants missing scores.</t>
-  </si>
-  <si>
-    <t>[TYPE_DATA INCORRECT] - ph_ch_anthro_average_bmi</t>
-  </si>
-  <si>
-    <t>The Data Dictionary element `type_data` for `average_bmi` will be corrected to `double` (currently=`character`).</t>
-  </si>
-  <si>
-    <t>Add DICOMs to release</t>
-  </si>
-  <si>
-    <t>Source DICOMs</t>
-  </si>
-  <si>
-    <t>Addition of source DICOMs for all imaging modalities.</t>
-  </si>
-  <si>
-    <t>Add in 'ANALYSIS DATE' for biospecimens</t>
-  </si>
-  <si>
     <t>data_warning</t>
   </si>
   <si>
@@ -569,7 +557,7 @@
     <t>MAPS-TL (&lt;1yr)</t>
   </si>
   <si>
-    <t>N=4 participants in `mh_cg_mapdb__inf` had no responses, but were scored 0; until resolved, set to null before analysis.</t>
+    <t>N=4 participants with no item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
   </si>
   <si>
     <t>[SCORING CORRECTION NEEDED]- EPDS</t>
@@ -578,7 +566,7 @@
     <t>EPDS</t>
   </si>
   <si>
-    <t>Some V01-V03 records show inconsistencies between item responses and the calculated sum score, including (1) items present, but sum score is null; (2) items null, but sum score is 0.</t>
+    <t>Inconsistent scoring: (1) item responses present, but score is null (N=1); (2) all items null, but score is `0` (N≥3).</t>
   </si>
   <si>
     <t>Anthro: ph_ch_anthro_head_for_age_boys_z_score</t>
@@ -608,7 +596,7 @@
     <t>[DD+DATA ERROR] Nail type field added for 2.0 all "Unknown"</t>
   </si>
   <si>
-    <t>Use `bio_bm_biosample_nails_typ_collection_nail_type` *specimen type* table for nail type (*results* table values are all 4 (Unknown)).</t>
+    <t>Nail type is `4` (Unknown) in the main results table (`*_nails_results`) and should be obtained from the specimen table (`*_nails_type`).</t>
   </si>
   <si>
     <t>[LORIS TO REVIEW]- pex_bm_healthv2_preg__exp__pnv_007__01 is completely blank</t>
@@ -662,6 +650,9 @@
     <t>Scanner Info</t>
   </si>
   <si>
+    <t>Scanner information must currently be parsed from raw BIDS data (specifically the scans .tsv files), as described [here](https://docs.hbcdstudy.org/latest/help/faq/#faq-scanner-info). Future releases will include a dedicated 'MRI Info' table that summarizes scanner information across participants, similar to the ABCD study ([see details](https://docs.abcdstudy.org/latest/documentation/imaging/admin.html#mr_y_adm__info)).</t>
+  </si>
+  <si>
     <t>RTDs ONLY - IGNORE</t>
   </si>
   <si>
@@ -671,19 +662,16 @@
     <t>patch_pending</t>
   </si>
   <si>
-    <t>Addition of age (`adjusted`/`gestational`/`candidate`) and `date_taken` fields (currently excluded due to use of *coding* rather than *visit* dates).</t>
+    <t>Add age (`adjusted`/`gestational`/`candidate`) and `date_taken` fields (currently excluded due to use of *coding* rather than *visit* dates).</t>
   </si>
   <si>
     <t>[DATA REQUEST]-household roster - sex variable</t>
   </si>
   <si>
-    <t>Demo</t>
-  </si>
-  <si>
-    <t>Addition of household roster fields capturing the sex of listed individuals for both adult &amp; child demographics tables.</t>
-  </si>
-  <si>
-    <t>[ADD DATA]-  raw Illumina .idat genetics data</t>
+    <t>Add household roster fields capturing the sex of listed individuals (adult &amp; child tables).</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]- anthro z-score calcs when no EDD/adjusted age available</t>
   </si>
   <si>
     <t>[DATA ERROR]-MLDS  total hours per week of non-parental hours</t>
@@ -701,7 +689,7 @@
     <t>BISQ-SF</t>
   </si>
   <si>
-    <t>Addition of Infant Sleep (IS) sub-scale score to `ph_cg_bisq`.</t>
+    <t>Add Infant Sleep (IS) sub-scale score to `ph_cg_bisq`.</t>
   </si>
   <si>
     <t>EEG file was not re-id'd (put in RTD) need to dig into how it happened -</t>
@@ -719,7 +707,7 @@
     <t>Vineland</t>
   </si>
   <si>
-    <t>Addition of language field to `ncl_cg_vabs`.</t>
+    <t>Add language field to `ncl_cg_vabs`.</t>
   </si>
   <si>
     <t>[DATA DICTIONARY CORRECTION]- MLDS  Â Â Â  special characters</t>
@@ -789,95 +777,13 @@
   </si>
   <si>
     <t>Raw BIDs include 2 corrupted bold runs in V02; view participant IDs/filepaths in the[HBCD Private Release Notes](https://hbcd-docs-private.lassoinformatics.com/#download).</t>
-  </si>
-  <si>
-    <t>Addition of creatinine results (`bio_creat_u`).</t>
-  </si>
-  <si>
-    <r>
-      <t>Scanner information must currently be parsed from raw BIDS data (specifically the scans .tsv files), as described [</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFCE9178"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>here</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFD4D4D4"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>](</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FFD4D4D4"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://docs.hbcdstudy.org/latest/help/faq/#faq-scanner-info</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFD4D4D4"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>). Future releases will include a dedicated 'MRI Info' table that summarizes scanner information across participants, similar to the ABCD study ([</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFCE9178"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>see details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFD4D4D4"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>](</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FFD4D4D4"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://docs.abcdstudy.org/latest/documentation/imaging/admin.html#mr_y_adm__info</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFD4D4D4"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>)).</t>
-    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -894,25 +800,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFD4D4D4"/>
-      <name val="Menlo"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFCE9178"/>
-      <name val="Menlo"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FFD4D4D4"/>
-      <name val="Menlo"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="21">
@@ -1030,7 +917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1095,7 +982,6 @@
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1435,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1847,14 +1733,14 @@
       <c r="H11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>20</v>
@@ -1862,7 +1748,7 @@
     </row>
     <row r="12" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -1900,7 +1786,7 @@
     </row>
     <row r="13" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1927,10 +1813,10 @@
         <v>17</v>
       </c>
       <c r="J13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>20</v>
@@ -1938,83 +1824,83 @@
     </row>
     <row r="14" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="C14" s="7">
+        <v>21.1</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>26</v>
+      <c r="L14" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
+      <c r="B15" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="C15" s="7">
+        <v>21.1</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>26</v>
+      <c r="F15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>26</v>
+        <v>70</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B16" s="7">
         <v>2.1</v>
@@ -2028,23 +1914,23 @@
       <c r="E16" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>16</v>
+      <c r="F16" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>20</v>
@@ -2052,37 +1938,37 @@
     </row>
     <row r="17" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B17" s="7">
         <v>2.1</v>
       </c>
       <c r="C17" s="7">
-        <v>21.1</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>77</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>17</v>
+      <c r="I17" s="21" t="s">
+        <v>78</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>20</v>
@@ -2090,7 +1976,7 @@
     </row>
     <row r="18" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B18" s="7">
         <v>2.1</v>
@@ -2101,26 +1987,26 @@
       <c r="D18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>16</v>
+      <c r="E18" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>20</v>
@@ -2128,7 +2014,7 @@
     </row>
     <row r="19" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B19" s="7">
         <v>2.1</v>
@@ -2139,26 +2025,26 @@
       <c r="D19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>34</v>
+      <c r="E19" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>20</v>
@@ -2166,7 +2052,7 @@
     </row>
     <row r="20" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B20" s="7">
         <v>2.1</v>
@@ -2175,28 +2061,28 @@
         <v>21</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>84</v>
+        <v>76</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>20</v>
@@ -2204,7 +2090,7 @@
     </row>
     <row r="21" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B21" s="7">
         <v>2.1</v>
@@ -2215,14 +2101,14 @@
       <c r="D21" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>90</v>
+      <c r="E21" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>77</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>34</v>
@@ -2231,10 +2117,10 @@
         <v>17</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>20</v>
@@ -2242,7 +2128,7 @@
     </row>
     <row r="22" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B22" s="7">
         <v>2.1</v>
@@ -2254,25 +2140,25 @@
         <v>13</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>16</v>
+        <v>68</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>20</v>
@@ -2280,7 +2166,7 @@
     </row>
     <row r="23" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B23" s="7">
         <v>2.1</v>
@@ -2291,14 +2177,14 @@
       <c r="D23" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>84</v>
+      <c r="E23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>34</v>
@@ -2307,10 +2193,10 @@
         <v>17</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>20</v>
@@ -2318,37 +2204,37 @@
     </row>
     <row r="24" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B24" s="7">
         <v>2.1</v>
       </c>
       <c r="C24" s="7">
-        <v>21.1</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>78</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>20</v>
@@ -2356,7 +2242,7 @@
     </row>
     <row r="25" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B25" s="7">
         <v>2.1</v>
@@ -2367,14 +2253,14 @@
       <c r="D25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>58</v>
+      <c r="E25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>34</v>
@@ -2383,10 +2269,10 @@
         <v>17</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>20</v>
@@ -2394,37 +2280,37 @@
     </row>
     <row r="26" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B26" s="7">
         <v>2.1</v>
       </c>
       <c r="C26" s="7">
-        <v>21</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>109</v>
+        <v>21.1</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="21" t="s">
-        <v>85</v>
+      <c r="I26" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>20</v>
@@ -2432,7 +2318,7 @@
     </row>
     <row r="27" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B27" s="7">
         <v>2.1</v>
@@ -2443,23 +2329,23 @@
       <c r="D27" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>34</v>
+      <c r="E27" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>113</v>
@@ -2482,16 +2368,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>34</v>
+      <c r="H28" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>17</v>
@@ -2520,25 +2406,25 @@
         <v>13</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>34</v>
+        <v>68</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>20</v>
@@ -2546,7 +2432,7 @@
     </row>
     <row r="30" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="7">
         <v>2.1</v>
@@ -2558,10 +2444,10 @@
         <v>13</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>33</v>
@@ -2573,10 +2459,10 @@
         <v>17</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>20</v>
@@ -2584,7 +2470,7 @@
     </row>
     <row r="31" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="7">
         <v>2.1</v>
@@ -2596,25 +2482,25 @@
         <v>13</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>16</v>
+        <v>68</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>258</v>
+        <v>124</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>20</v>
@@ -2622,7 +2508,7 @@
     </row>
     <row r="32" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" s="7">
         <v>2.1</v>
@@ -2634,22 +2520,22 @@
         <v>13</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>16</v>
+        <v>68</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="K32" s="7" t="s">
         <v>126</v>
@@ -2672,13 +2558,13 @@
         <v>13</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>58</v>
+        <v>68</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>40</v>
@@ -2687,7 +2573,7 @@
         <v>17</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>128</v>
@@ -2703,32 +2589,32 @@
       <c r="B34" s="7">
         <v>2.1</v>
       </c>
-      <c r="C34" s="7">
-        <v>21.1</v>
+      <c r="C34" t="s">
+        <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>40</v>
+        <v>68</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>20</v>
@@ -2736,37 +2622,37 @@
     </row>
     <row r="35" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="7">
-        <v>2.1</v>
-      </c>
-      <c r="C35" s="7">
-        <v>21.1</v>
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>40</v>
+      <c r="E35" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>20</v>
@@ -2774,10 +2660,10 @@
     </row>
     <row r="36" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B36" s="7">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
@@ -2785,8 +2671,8 @@
       <c r="D36" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="19" t="s">
-        <v>72</v>
+      <c r="E36" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="F36" s="14" t="s">
         <v>44</v>
@@ -2801,10 +2687,10 @@
         <v>17</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>20</v>
@@ -2812,7 +2698,7 @@
     </row>
     <row r="37" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B37" s="7">
         <v>3</v>
@@ -2823,26 +2709,26 @@
       <c r="D37" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>34</v>
+      <c r="E37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>20</v>
@@ -2850,7 +2736,7 @@
     </row>
     <row r="38" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="7">
         <v>3</v>
@@ -2877,10 +2763,10 @@
         <v>17</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>20</v>
@@ -2888,7 +2774,7 @@
     </row>
     <row r="39" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="7">
         <v>3</v>
@@ -2899,34 +2785,34 @@
       <c r="D39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>17</v>
+      <c r="E39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>145</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>20</v>
+        <v>147</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B40" s="7">
         <v>3</v>
@@ -2937,26 +2823,26 @@
       <c r="D40" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>16</v>
+      <c r="E40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>20</v>
@@ -2964,7 +2850,7 @@
     </row>
     <row r="41" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B41" s="7">
         <v>3</v>
@@ -2978,31 +2864,31 @@
       <c r="E41" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I41" s="18" t="s">
-        <v>150</v>
+      <c r="F41" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>26</v>
+        <v>153</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="7">
         <v>3</v>
@@ -3016,23 +2902,23 @@
       <c r="E42" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>34</v>
+      <c r="F42" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L42" s="6" t="s">
         <v>20</v>
@@ -3040,7 +2926,7 @@
     </row>
     <row r="43" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="7">
         <v>3</v>
@@ -3051,14 +2937,14 @@
       <c r="D43" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>39</v>
+      <c r="E43" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>16</v>
@@ -3067,7 +2953,7 @@
         <v>17</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>158</v>
@@ -3092,14 +2978,14 @@
       <c r="E44" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F44" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G44" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>16</v>
+      <c r="F44" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>17</v>
@@ -3127,14 +3013,14 @@
       <c r="D45" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E45" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F45" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G45" s="14" t="s">
-        <v>44</v>
+      <c r="E45" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>16</v>
@@ -3143,10 +3029,10 @@
         <v>17</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L45" s="6" t="s">
         <v>20</v>
@@ -3154,7 +3040,7 @@
     </row>
     <row r="46" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" s="7">
         <v>3</v>
@@ -3168,11 +3054,11 @@
       <c r="E46" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F46" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>39</v>
+      <c r="F46" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="H46" s="8" t="s">
         <v>34</v>
@@ -3181,7 +3067,7 @@
         <v>17</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>165</v>
+        <v>45</v>
       </c>
       <c r="K46" s="7" t="s">
         <v>166</v>
@@ -3206,14 +3092,14 @@
       <c r="E47" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F47" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>34</v>
+      <c r="F47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>17</v>
@@ -3241,34 +3127,34 @@
       <c r="D48" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>34</v>
+      <c r="E48" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>172</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="L48" s="12" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B49" s="7">
         <v>3</v>
@@ -3279,14 +3165,14 @@
       <c r="D49" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>15</v>
+      <c r="E49" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>16</v>
@@ -3295,10 +3181,10 @@
         <v>17</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L49" s="6" t="s">
         <v>20</v>
@@ -3306,7 +3192,7 @@
     </row>
     <row r="50" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B50" s="7">
         <v>3</v>
@@ -3317,34 +3203,34 @@
       <c r="D50" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E50" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G50" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="H50" s="18" t="s">
-        <v>176</v>
+      <c r="E50" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L50" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B51" s="7">
         <v>3</v>
@@ -3355,26 +3241,26 @@
       <c r="D51" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E51" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>16</v>
+      <c r="E51" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L51" s="6" t="s">
         <v>20</v>
@@ -3382,7 +3268,7 @@
     </row>
     <row r="52" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B52" s="7">
         <v>3</v>
@@ -3396,11 +3282,11 @@
       <c r="E52" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F52" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G52" s="11" t="s">
-        <v>39</v>
+      <c r="F52" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>34</v>
@@ -3409,10 +3295,10 @@
         <v>17</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>20</v>
@@ -3420,7 +3306,7 @@
     </row>
     <row r="53" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="7">
         <v>3</v>
@@ -3435,10 +3321,10 @@
         <v>32</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H53" s="8" t="s">
         <v>34</v>
@@ -3447,10 +3333,10 @@
         <v>17</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L53" s="6" t="s">
         <v>20</v>
@@ -3458,7 +3344,7 @@
     </row>
     <row r="54" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="7">
         <v>3</v>
@@ -3469,26 +3355,26 @@
       <c r="D54" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F54" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>34</v>
+      <c r="E54" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L54" s="6" t="s">
         <v>20</v>
@@ -3496,10 +3382,10 @@
     </row>
     <row r="55" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B55" s="7">
-        <v>3</v>
+        <v>192</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
@@ -3507,14 +3393,14 @@
       <c r="D55" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E55" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>90</v>
+      <c r="E55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>77</v>
       </c>
       <c r="H55" s="8" t="s">
         <v>34</v>
@@ -3523,10 +3409,10 @@
         <v>17</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>191</v>
+        <v>94</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L55" s="6" t="s">
         <v>20</v>
@@ -3534,10 +3420,10 @@
     </row>
     <row r="56" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B56" s="7">
-        <v>3</v>
+        <v>194</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -3545,26 +3431,26 @@
       <c r="D56" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G56" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>16</v>
+      <c r="E56" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L56" s="6" t="s">
         <v>20</v>
@@ -3572,7 +3458,7 @@
     </row>
     <row r="57" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -3583,14 +3469,14 @@
       <c r="D57" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F57" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G57" s="20" t="s">
-        <v>84</v>
+      <c r="E57" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="H57" s="8" t="s">
         <v>34</v>
@@ -3599,10 +3485,10 @@
         <v>17</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>98</v>
+        <v>195</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L57" s="6" t="s">
         <v>20</v>
@@ -3610,10 +3496,10 @@
     </row>
     <row r="58" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B58" t="s">
-        <v>13</v>
+        <v>199</v>
+      </c>
+      <c r="B58" s="7">
+        <v>3</v>
       </c>
       <c r="C58" t="s">
         <v>13</v>
@@ -3621,26 +3507,26 @@
       <c r="D58" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E58" s="8" t="s">
-        <v>22</v>
+      <c r="E58" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H58" s="8" t="s">
-        <v>34</v>
+        <v>83</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L58" s="6" t="s">
         <v>20</v>
@@ -3648,10 +3534,10 @@
     </row>
     <row r="59" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B59" t="s">
-        <v>13</v>
+        <v>202</v>
+      </c>
+      <c r="B59" s="7">
+        <v>3</v>
       </c>
       <c r="C59" t="s">
         <v>13</v>
@@ -3662,26 +3548,26 @@
       <c r="E59" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>17</v>
+      <c r="F59" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>199</v>
+        <v>41</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3700,31 +3586,31 @@
       <c r="E60" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F60" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>17</v>
+      <c r="F60" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G60" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>204</v>
+        <v>13</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B61" s="7">
         <v>3</v>
@@ -3735,29 +3621,29 @@
       <c r="D61" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E61" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G61" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>26</v>
+      <c r="E61" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>41</v>
+        <v>205</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>26</v>
+        <v>206</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3776,31 +3662,31 @@
       <c r="E62" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F62" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G62" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>26</v>
+      <c r="F62" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>13</v>
+        <v>146</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>26</v>
+        <v>208</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B63" s="7">
         <v>3</v>
@@ -3811,26 +3697,26 @@
       <c r="D63" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F63" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G63" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H63" s="8" t="s">
-        <v>34</v>
+      <c r="E63" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L63" s="6" t="s">
         <v>20</v>
@@ -3838,7 +3724,7 @@
     </row>
     <row r="64" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B64" s="7">
         <v>3</v>
@@ -3849,26 +3735,26 @@
       <c r="D64" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>34</v>
+      <c r="E64" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H64" s="19" t="s">
+        <v>214</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="L64" s="6" t="s">
         <v>20</v>
@@ -3876,7 +3762,7 @@
     </row>
     <row r="65" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B65" s="7">
         <v>3</v>
@@ -3890,11 +3776,11 @@
       <c r="E65" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>15</v>
+      <c r="F65" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>16</v>
@@ -3903,10 +3789,10 @@
         <v>17</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="K65" s="22" t="s">
-        <v>259</v>
+        <v>59</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>217</v>
       </c>
       <c r="L65" s="6" t="s">
         <v>20</v>
@@ -3914,10 +3800,10 @@
     </row>
     <row r="66" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B66" s="7">
-        <v>3</v>
+        <v>218</v>
+      </c>
+      <c r="B66" t="s">
+        <v>13</v>
       </c>
       <c r="C66" t="s">
         <v>13</v>
@@ -3925,37 +3811,37 @@
       <c r="D66" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E66" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G66" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H66" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>17</v>
+      <c r="E66" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B67" s="7">
-        <v>3</v>
+      <c r="B67" t="s">
+        <v>13</v>
       </c>
       <c r="C67" t="s">
         <v>13</v>
@@ -3966,14 +3852,14 @@
       <c r="E67" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F67" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G67" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>16</v>
+      <c r="F67" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>17</v>
@@ -4001,64 +3887,64 @@
       <c r="D68" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>26</v>
+      <c r="E68" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>13</v>
+        <v>223</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>26</v>
+        <v>224</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B69" t="s">
-        <v>13</v>
-      </c>
-      <c r="C69" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F69" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>94</v>
+        <v>225</v>
+      </c>
+      <c r="B69" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="C69" s="7">
+        <v>21.1</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="H69" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I69" s="6" t="s">
-        <v>17</v>
+      <c r="I69" s="21" t="s">
+        <v>78</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L69" s="6" t="s">
         <v>20</v>
@@ -4066,37 +3952,37 @@
     </row>
     <row r="70" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B70" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F70" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="14" t="s">
-        <v>44</v>
+        <v>228</v>
+      </c>
+      <c r="B70" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="C70" s="7">
+        <v>21</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I70" s="6" t="s">
-        <v>17</v>
+      <c r="I70" s="21" t="s">
+        <v>78</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L70" s="6" t="s">
         <v>20</v>
@@ -4104,37 +3990,37 @@
     </row>
     <row r="71" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B71" s="7">
         <v>2.1</v>
       </c>
       <c r="C71" s="7">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F71" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G71" s="15" t="s">
-        <v>79</v>
+      <c r="F71" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="H71" s="8" t="s">
         <v>34</v>
       </c>
       <c r="I71" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L71" s="6" t="s">
         <v>20</v>
@@ -4142,7 +4028,7 @@
     </row>
     <row r="72" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B72" s="7">
         <v>2.1</v>
@@ -4151,25 +4037,25 @@
         <v>21</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F72" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G72" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>16</v>
+      <c r="F72" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G72" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I72" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>233</v>
+        <v>59</v>
       </c>
       <c r="K72" s="7" t="s">
         <v>234</v>
@@ -4189,28 +4075,28 @@
         <v>21</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F73" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G73" s="16" t="s">
-        <v>94</v>
+      <c r="F73" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>77</v>
       </c>
       <c r="H73" s="8" t="s">
         <v>34</v>
       </c>
       <c r="I73" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L73" s="6" t="s">
         <v>20</v>
@@ -4218,7 +4104,7 @@
     </row>
     <row r="74" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B74" s="7">
         <v>2.1</v>
@@ -4227,28 +4113,28 @@
         <v>21</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F74" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G74" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>34</v>
+      <c r="F74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I74" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L74" s="6" t="s">
         <v>20</v>
@@ -4256,7 +4142,7 @@
     </row>
     <row r="75" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B75" s="7">
         <v>2.1</v>
@@ -4265,28 +4151,28 @@
         <v>21</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F75" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G75" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>34</v>
+      <c r="F75" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="I75" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>240</v>
+        <v>41</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L75" s="6" t="s">
         <v>20</v>
@@ -4294,7 +4180,7 @@
     </row>
     <row r="76" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B76" s="7">
         <v>2.1</v>
@@ -4303,28 +4189,28 @@
         <v>21</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>15</v>
+      <c r="F76" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G76" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="H76" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I76" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L76" s="6" t="s">
         <v>20</v>
@@ -4332,7 +4218,7 @@
     </row>
     <row r="77" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B77" s="7">
         <v>2.1</v>
@@ -4341,28 +4227,28 @@
         <v>21</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F77" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G77" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>16</v>
+      <c r="F77" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G77" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I77" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>41</v>
+        <v>229</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L77" s="6" t="s">
         <v>20</v>
@@ -4370,7 +4256,7 @@
     </row>
     <row r="78" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B78" s="7">
         <v>2.1</v>
@@ -4379,28 +4265,28 @@
         <v>21</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F78" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G78" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>16</v>
+      <c r="F78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="I78" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L78" s="6" t="s">
         <v>20</v>
@@ -4408,7 +4294,7 @@
     </row>
     <row r="79" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B79" s="7">
         <v>2.1</v>
@@ -4417,106 +4303,30 @@
         <v>21</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F79" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G79" s="16" t="s">
-        <v>94</v>
+      <c r="F79" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="H79" s="8" t="s">
         <v>34</v>
       </c>
       <c r="I79" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B80" s="7">
-        <v>2.1</v>
-      </c>
-      <c r="C80" s="7">
-        <v>21</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I80" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="J80" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="K80" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B81" s="7">
-        <v>2.1</v>
-      </c>
-      <c r="C81" s="7">
-        <v>21</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H81" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I81" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="J81" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="K81" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="L81" s="6" t="s">
         <v>20</v>
       </c>
     </row>

--- a/tools/latest.xlsx
+++ b/tools/latest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10911"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D458A66-823B-8946-89F5-2B25D1C11D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2E07A9-077B-7643-A314-915E817C6592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🤩 public data release" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="249">
   <si>
     <t>Name</t>
   </si>
@@ -128,27 +128,27 @@
     <t>Anthro: LT goal for implementing score calculation in ETL based on EDD</t>
   </si>
   <si>
+    <t>21.1</t>
+  </si>
+  <si>
+    <t>Physical Health</t>
+  </si>
+  <si>
+    <t>Archived to BR</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>Add age-based z-scores to `ph_ch_anthro` (see [Z-Scores Excluded](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
+  </si>
+  <si>
+    <t>Genomics - OLINK data proteomics</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Waiting on WG feedback</t>
-  </si>
-  <si>
-    <t>Physical Health</t>
-  </si>
-  <si>
-    <t>Archived to BR</t>
-  </si>
-  <si>
-    <t>Growth</t>
-  </si>
-  <si>
-    <t>Add age-based z-scores to `ph_ch_anthro` (see [Z-Scores Excluded](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
-  </si>
-  <si>
-    <t>Genomics - OLINK data proteomics</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -161,21 +161,6 @@
     <t>Add Olink Explore 384 Inflammation 1 Panel, proteomics measure of maternal inflammation during pregnancy</t>
   </si>
   <si>
-    <t>Bayley item-level scores</t>
-  </si>
-  <si>
-    <t>21.1</t>
-  </si>
-  <si>
-    <t>Neurocognition &amp; Language</t>
-  </si>
-  <si>
-    <t>Bayley-4</t>
-  </si>
-  <si>
-    <t>Add item-level scores.</t>
-  </si>
-  <si>
     <t>[DATA ERROR]- Study Navigator blank checkboxes</t>
   </si>
   <si>
@@ -234,9 +219,6 @@
   </si>
   <si>
     <t>[DATA ERROR]- PA/greenspace type_Data= text so breaking lasso dashboard</t>
-  </si>
-  <si>
-    <t>LORIS reviewing</t>
   </si>
   <si>
     <t>ecPROMIS-PAGS</t>
@@ -321,7 +303,7 @@
     <t>Not started yet</t>
   </si>
   <si>
-    <t>The Data Dictionary element `type_data` for `average_bmi` will be corrected to `double` (currently=`character`).</t>
+    <t>The data dictionary element `type_data` for `average_bmi` will be corrected to `double` (currently=`character`).</t>
   </si>
   <si>
     <t>Add DICOMs to release</t>
@@ -369,90 +351,93 @@
     <t>Inclusion of Blood Spot Card Results data from USDTL.</t>
   </si>
   <si>
+    <t>DD 'instruction' field all blank</t>
+  </si>
+  <si>
+    <t>Instruction</t>
+  </si>
+  <si>
+    <t>The 'instruction' data dictionary element is currently blank.</t>
+  </si>
+  <si>
+    <t>Followup item: scanner info</t>
+  </si>
+  <si>
+    <t>Scanner Info</t>
+  </si>
+  <si>
+    <t>Scanner information must currently be parsed from raw BIDS data (specifically the scans .tsv files), as described [here](https://docs.hbcdstudy.org/latest/help/faq/#faq-scanner-info). Future releases will include a dedicated 'MRI Info' table that summarizes scanner information across participants, similar to the ABCD study ([see details](https://docs.abcdstudy.org/latest/documentation/imaging/admin.html#mr_y_adm__info)).</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST] ERICA - add age &amp; date_taken fields back to ERICA once corrected (post 2.1 patch)</t>
+  </si>
+  <si>
+    <t>Add all age and `date_taken` fields (currently excluded due to use of coding rather than visit dates).</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- ecPROMIS child-caregiver infant</t>
+  </si>
+  <si>
+    <t>ecPROMIS CC</t>
+  </si>
+  <si>
+    <t>N=12 V03 participants with &lt;3 item responses are incorrectly scored as `0` in `mh_cg_pms__cc__inf`; set values to null prior to analysis.</t>
+  </si>
+  <si>
+    <t>[IMAGING] Add Cook's distance to tabulated imaging data</t>
+  </si>
+  <si>
+    <t>Cook's Distance</t>
+  </si>
+  <si>
+    <t>Addition Cook's distance values computed for fMRI.</t>
+  </si>
+  <si>
+    <t>[2.0 SCORING CORRECTION NEEDED]- V03 MAPS-TL</t>
+  </si>
+  <si>
+    <t>MAPS-TL (&lt;1yr)</t>
+  </si>
+  <si>
+    <t>N=4 participants with no item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
+  </si>
+  <si>
+    <t>[SCORING CORRECTION NEEDED]- EPDS</t>
+  </si>
+  <si>
+    <t>LORIS reviewing</t>
+  </si>
+  <si>
+    <t>EPDS</t>
+  </si>
+  <si>
+    <t>Inconsistent scoring: (1) item responses present, but score is null (N=1); (2) all items null, but score is `0` (N≥3).</t>
+  </si>
+  <si>
+    <t>Anthro: ph_ch_anthro_head_for_age_boys_z_score</t>
+  </si>
+  <si>
+    <t>Growth (`ph_ch_anthro`) filter ranges will be updated to be visit-specific, as current ranges allow biologically implausible values (see [Range Checks](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]-household roster - sex variable</t>
+  </si>
+  <si>
+    <t>Demo</t>
+  </si>
+  <si>
+    <t>Add household roster fields capturing the sex of listed individuals (adult &amp; child tables).</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]- anthro z-score calcs when no EDD/adjusted age available</t>
+  </si>
+  <si>
+    <t>on hold/later</t>
+  </si>
+  <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>DD 'instruction' field all blank</t>
-  </si>
-  <si>
-    <t>Instruction</t>
-  </si>
-  <si>
-    <t>The 'instruction' Data Dictionary element is currently blank.</t>
-  </si>
-  <si>
-    <t>Followup item: scanner info</t>
-  </si>
-  <si>
-    <t>Scanner Info</t>
-  </si>
-  <si>
-    <t>Scanner information must currently be parsed from raw BIDS data (specifically the scans .tsv files), as described [here](https://docs.hbcdstudy.org/latest/help/faq/#faq-scanner-info). Future releases will include a dedicated 'MRI Info' table that summarizes scanner information across participants, similar to the ABCD study ([see details](https://docs.abcdstudy.org/latest/documentation/imaging/admin.html#mr_y_adm__info)).</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST] ERICA - add age &amp; date_taken fields back to ERICA once corrected (post 2.1 patch)</t>
-  </si>
-  <si>
-    <t>Add all age and `date_taken` fields (currently excluded due to use of coding rather than visit dates).</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- ecPROMIS child-caregiver infant</t>
-  </si>
-  <si>
-    <t>ecPROMIS CC</t>
-  </si>
-  <si>
-    <t>N=12 V03 participants with &lt;3 item responses are incorrectly scored as `0` in `mh_cg_pms__cc__inf`; set values to null prior to analysis.</t>
-  </si>
-  <si>
-    <t>[IMAGING] Add Cook's distance to tabulated imaging data</t>
-  </si>
-  <si>
-    <t>Cook's Distance</t>
-  </si>
-  <si>
-    <t>Addition Cook's distance values computed for fMRI.</t>
-  </si>
-  <si>
-    <t>[2.0 SCORING CORRECTION NEEDED]- V03 MAPS-TL</t>
-  </si>
-  <si>
-    <t>MAPS-TL (&lt;1yr)</t>
-  </si>
-  <si>
-    <t>N=4 participants with no item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
-  </si>
-  <si>
-    <t>[SCORING CORRECTION NEEDED]- EPDS</t>
-  </si>
-  <si>
-    <t>EPDS</t>
-  </si>
-  <si>
-    <t>Inconsistent scoring: (1) item responses present, but score is null (N=1); (2) all items null, but score is `0` (N≥3).</t>
-  </si>
-  <si>
-    <t>Anthro: ph_ch_anthro_head_for_age_boys_z_score</t>
-  </si>
-  <si>
-    <t>Growth (`ph_ch_anthro`) filter ranges will be updated to be visit-specific, as current ranges allow biologically implausible values (see [Range Checks](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]-household roster - sex variable</t>
-  </si>
-  <si>
-    <t>Demo</t>
-  </si>
-  <si>
-    <t>Add household roster fields capturing the sex of listed individuals (adult &amp; child tables).</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- anthro z-score calcs when no EDD/adjusted age available</t>
-  </si>
-  <si>
-    <t>on hold/later</t>
-  </si>
-  <si>
     <t>[DATA ERROR]- missing sleep score fields- ecPROMIS SLEEP</t>
   </si>
   <si>
@@ -501,6 +486,9 @@
     <t>EEG</t>
   </si>
   <si>
+    <t>Age fields</t>
+  </si>
+  <si>
     <t>Chronological and adjusted age fall outside of 3-9 months in N=74 V03 sessions (site entry errors); exclude age values prior to analysis.</t>
   </si>
   <si>
@@ -513,6 +501,30 @@
     <t>PNR data were incorrectly reported using TLFB versions 1/2 and will be updated to [version 3 specific to PNR](https://docs.hbcdstudy.org/latest/instruments/pregexp/su/tlfb/#v3).</t>
   </si>
   <si>
+    <t>Gabi raw BIDs</t>
+  </si>
+  <si>
+    <t>New; needs discussion</t>
+  </si>
+  <si>
+    <t>Novel Tech &amp; Wearable Sensors</t>
+  </si>
+  <si>
+    <t>GABI</t>
+  </si>
+  <si>
+    <t>Addition of raw BIDS data for GABI (infant heart rate).</t>
+  </si>
+  <si>
+    <t>[POSSIBLE DATA ERROR]- roster at V02 or V03</t>
+  </si>
+  <si>
+    <t>Started, outprioritized</t>
+  </si>
+  <si>
+    <t>Roster was inappropriately collected at V02/V03 for all cohorts and should have been restricted to V02 PNRs and alternate caregiver cohorts; to be excluded.</t>
+  </si>
+  <si>
     <t>Remove 'sequence' field from all tables in Lasso</t>
   </si>
   <si>
@@ -525,6 +537,9 @@
     <t>[DATA ERROR]-MLDS  total hours per week of non-parental hours</t>
   </si>
   <si>
+    <t>Neurocognition &amp; Language</t>
+  </si>
+  <si>
     <t>MLDS</t>
   </si>
   <si>
@@ -565,6 +580,9 @@
   </si>
   <si>
     <t>BISQR: infant sleep score - need to add</t>
+  </si>
+  <si>
+    <t>Waiting on WG feedback</t>
   </si>
   <si>
     <t>BISQ-SF</t>
@@ -770,7 +788,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -819,12 +837,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4C4C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF563E3E"/>
+        <fgColor rgb="FFFAA1F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -839,12 +852,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCB00"/>
+        <fgColor rgb="FFC4C4C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAA1F1"/>
+        <fgColor rgb="FFFFCB00"/>
       </patternFill>
     </fill>
     <fill>
@@ -877,6 +890,21 @@
         <fgColor rgb="FFCAB641"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF037F4C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF563E3E"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -890,7 +918,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -956,6 +984,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1297,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1527,23 +1561,23 @@
       <c r="D7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>19</v>
@@ -1551,16 +1585,16 @@
     </row>
     <row r="8" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>44</v>
@@ -1571,8 +1605,8 @@
       <c r="G8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="14" t="s">
-        <v>40</v>
+      <c r="H8" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>46</v>
@@ -1592,22 +1626,22 @@
         <v>2.1</v>
       </c>
       <c r="C9" s="3">
-        <v>21.1</v>
-      </c>
-      <c r="D9" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="13" t="s">
         <v>50</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="14" t="s">
-        <v>40</v>
+      <c r="H9" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>51</v>
@@ -1627,28 +1661,28 @@
         <v>2.1</v>
       </c>
       <c r="C10" s="3">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>55</v>
+      <c r="E10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="14" t="s">
-        <v>40</v>
+      <c r="H10" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>19</v>
@@ -1656,7 +1690,7 @@
     </row>
     <row r="11" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B11" s="3">
         <v>2.1</v>
@@ -1667,23 +1701,23 @@
       <c r="D11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>45</v>
+      <c r="E11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="14" t="s">
-        <v>40</v>
+      <c r="H11" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>19</v>
@@ -1691,7 +1725,7 @@
     </row>
     <row r="12" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B12" s="3">
         <v>2.1</v>
@@ -1699,26 +1733,26 @@
       <c r="C12" s="3">
         <v>21.1</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>14</v>
+      <c r="D12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="14" t="s">
-        <v>40</v>
+      <c r="H12" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>19</v>
@@ -1726,13 +1760,13 @@
     </row>
     <row r="13" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="3">
         <v>2.1</v>
       </c>
       <c r="C13" s="3">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>12</v>
@@ -1741,19 +1775,19 @@
         <v>13</v>
       </c>
       <c r="F13" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>19</v>
@@ -1761,7 +1795,7 @@
     </row>
     <row r="14" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" s="3">
         <v>2.1</v>
@@ -1772,23 +1806,23 @@
       <c r="D14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="19" t="s">
+      <c r="E14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>19</v>
@@ -1796,22 +1830,22 @@
     </row>
     <row r="15" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B15" s="3">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>15</v>
@@ -1820,10 +1854,10 @@
         <v>16</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>19</v>
@@ -1831,34 +1865,34 @@
     </row>
     <row r="16" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>15</v>
+      <c r="F16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>19</v>
@@ -1866,16 +1900,16 @@
     </row>
     <row r="17" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B17" s="3">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>44</v>
@@ -1890,10 +1924,10 @@
         <v>16</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>19</v>
@@ -1901,34 +1935,34 @@
     </row>
     <row r="18" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B18" s="3">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>21</v>
+      <c r="F18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>19</v>
@@ -1936,34 +1970,34 @@
     </row>
     <row r="19" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B19" s="3">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>84</v>
+      <c r="F19" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>19</v>
@@ -1971,34 +2005,34 @@
     </row>
     <row r="20" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B20" s="3">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>15</v>
+      <c r="F20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>19</v>
@@ -2006,16 +2040,16 @@
     </row>
     <row r="21" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B21" s="3">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>44</v>
@@ -2030,10 +2064,10 @@
         <v>16</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>19</v>
@@ -2041,16 +2075,16 @@
     </row>
     <row r="22" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B22" s="3">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>44</v>
@@ -2058,17 +2092,17 @@
       <c r="F22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>21</v>
+      <c r="G22" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>19</v>
@@ -2076,34 +2110,34 @@
     </row>
     <row r="23" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B23" s="3">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>19</v>
@@ -2111,34 +2145,34 @@
     </row>
     <row r="24" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>21</v>
+        <v>43</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>19</v>
@@ -2146,22 +2180,22 @@
     </row>
     <row r="25" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B25" s="3">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>65</v>
+        <v>43</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>15</v>
@@ -2170,10 +2204,10 @@
         <v>16</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>19</v>
@@ -2181,34 +2215,34 @@
     </row>
     <row r="26" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B26" s="3">
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K26" s="7" t="s">
         <v>19</v>
@@ -2216,34 +2250,34 @@
     </row>
     <row r="27" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B27" s="3">
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>21</v>
+        <v>43</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>19</v>
@@ -2251,22 +2285,22 @@
     </row>
     <row r="28" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B28" s="3">
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>15</v>
@@ -2275,10 +2309,10 @@
         <v>16</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K28" s="7" t="s">
         <v>19</v>
@@ -2286,69 +2320,69 @@
     </row>
     <row r="29" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B29" s="3">
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B30" s="3">
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>21</v>
+        <v>43</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>19</v>
@@ -2356,34 +2390,34 @@
     </row>
     <row r="31" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B31" s="3">
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>19</v>
@@ -2391,34 +2425,34 @@
     </row>
     <row r="32" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B32" s="3">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>100</v>
+        <v>43</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>84</v>
+      <c r="G32" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K32" s="7" t="s">
         <v>19</v>
@@ -2426,34 +2460,34 @@
     </row>
     <row r="33" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B33" s="3">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>21</v>
+        <v>43</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>19</v>
@@ -2461,57 +2495,57 @@
     </row>
     <row r="34" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B34" s="3">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K34" s="11" t="s">
-        <v>117</v>
+        <v>127</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B35" s="3">
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>25</v>
+        <v>43</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>21</v>
@@ -2520,10 +2554,10 @@
         <v>16</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>19</v>
@@ -2531,22 +2565,22 @@
     </row>
     <row r="36" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B36" s="3">
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>21</v>
@@ -2555,10 +2589,10 @@
         <v>16</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>19</v>
@@ -2566,34 +2600,34 @@
     </row>
     <row r="37" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B37" s="3">
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>21</v>
+        <v>43</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>19</v>
@@ -2601,104 +2635,104 @@
     </row>
     <row r="38" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B38" s="3">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>16</v>
+        <v>43</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K38" s="7" t="s">
-        <v>19</v>
+        <v>43</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B39" s="3">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>117</v>
+        <v>43</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>117</v>
+        <v>142</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B40" s="3">
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>19</v>
@@ -2706,22 +2740,22 @@
     </row>
     <row r="41" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B41" s="3">
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F41" s="20" t="s">
-        <v>87</v>
+      <c r="F41" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>21</v>
@@ -2730,10 +2764,10 @@
         <v>16</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>149</v>
+        <v>40</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>19</v>
@@ -2741,101 +2775,101 @@
     </row>
     <row r="42" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B42" s="3">
         <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>16</v>
+        <v>43</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>19</v>
+        <v>43</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B43" s="3">
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="G43" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>117</v>
+        <v>43</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K43" s="11" t="s">
-        <v>117</v>
+        <v>152</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="B44" s="3">
-        <v>3</v>
-      </c>
-      <c r="C44" t="s">
-        <v>37</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>157</v>
@@ -2849,31 +2883,31 @@
         <v>158</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F45" s="22" t="s">
+      <c r="J45" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>19</v>
@@ -2881,34 +2915,34 @@
     </row>
     <row r="46" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B46" s="3">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E46" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="B46" t="s">
-        <v>37</v>
-      </c>
-      <c r="C46" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>21</v>
+      <c r="F46" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K46" s="7" t="s">
         <v>19</v>
@@ -2916,34 +2950,34 @@
     </row>
     <row r="47" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B47" t="s">
-        <v>37</v>
+        <v>166</v>
+      </c>
+      <c r="B47" s="3">
+        <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>19</v>
@@ -2951,34 +2985,34 @@
     </row>
     <row r="48" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C48" t="s">
-        <v>37</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>21</v>
+        <v>43</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K48" s="7" t="s">
         <v>19</v>
@@ -2986,72 +3020,72 @@
     </row>
     <row r="49" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>37</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>87</v>
+        <v>43</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H49" s="19" t="s">
-        <v>172</v>
+      <c r="H49" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K49" s="11" t="s">
-        <v>117</v>
+        <v>175</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C50" t="s">
-        <v>37</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>16</v>
+        <v>43</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>177</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K50" s="4" t="s">
         <v>178</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3059,54 +3093,54 @@
         <v>179</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C51" t="s">
-        <v>37</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G51" s="18" t="s">
+        <v>181</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>19</v>
+        <v>43</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C52" t="s">
-        <v>37</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E52" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F52" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>15</v>
@@ -3115,10 +3149,10 @@
         <v>16</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K52" s="7" t="s">
         <v>19</v>
@@ -3126,34 +3160,34 @@
     </row>
     <row r="53" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C53" t="s">
-        <v>37</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F53" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>21</v>
+        <v>43</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>19</v>
@@ -3161,34 +3195,34 @@
     </row>
     <row r="54" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C54" t="s">
-        <v>37</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K54" s="7" t="s">
         <v>19</v>
@@ -3196,34 +3230,34 @@
     </row>
     <row r="55" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B55" s="3">
-        <v>2.1</v>
-      </c>
-      <c r="C55" s="3">
-        <v>21.1</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>40</v>
+        <v>194</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>19</v>
@@ -3231,34 +3265,34 @@
     </row>
     <row r="56" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B56" s="3">
         <v>2.1</v>
       </c>
       <c r="C56" s="3">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F56" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H56" s="14" t="s">
-        <v>40</v>
+      <c r="F56" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K56" s="7" t="s">
         <v>19</v>
@@ -3266,7 +3300,7 @@
     </row>
     <row r="57" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B57" s="3">
         <v>2.1</v>
@@ -3275,33 +3309,33 @@
         <v>21</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F57" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G57" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>40</v>
+      <c r="F57" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>178</v>
+        <v>203</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B58" s="3">
         <v>2.1</v>
@@ -3310,33 +3344,33 @@
         <v>21</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F58" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H58" s="14" t="s">
-        <v>40</v>
+      <c r="F58" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="G58" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="K58" s="7" t="s">
-        <v>19</v>
+        <v>206</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B59" s="3">
         <v>2.1</v>
@@ -3345,25 +3379,25 @@
         <v>21</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F59" s="15" t="s">
-        <v>45</v>
+      <c r="F59" s="18" t="s">
+        <v>64</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H59" s="14" t="s">
-        <v>40</v>
+      <c r="H59" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K59" s="7" t="s">
         <v>19</v>
@@ -3371,7 +3405,7 @@
     </row>
     <row r="60" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B60" s="3">
         <v>2.1</v>
@@ -3380,25 +3414,25 @@
         <v>21</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F60" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H60" s="14" t="s">
-        <v>40</v>
+      <c r="F60" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K60" s="7" t="s">
         <v>19</v>
@@ -3406,7 +3440,7 @@
     </row>
     <row r="61" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B61" s="3">
         <v>2.1</v>
@@ -3415,25 +3449,25 @@
         <v>21</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>25</v>
+      <c r="F61" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H61" s="14" t="s">
-        <v>40</v>
+      <c r="H61" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K61" s="7" t="s">
         <v>19</v>
@@ -3441,7 +3475,7 @@
     </row>
     <row r="62" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B62" s="3">
         <v>2.1</v>
@@ -3450,25 +3484,25 @@
         <v>21</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F62" s="19" t="s">
-        <v>69</v>
+      <c r="F62" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H62" s="14" t="s">
-        <v>40</v>
+      <c r="H62" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>212</v>
+        <v>27</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K62" s="7" t="s">
         <v>19</v>
@@ -3476,7 +3510,7 @@
     </row>
     <row r="63" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B63" s="3">
         <v>2.1</v>
@@ -3485,25 +3519,25 @@
         <v>21</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F63" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H63" s="14" t="s">
-        <v>40</v>
+      <c r="F63" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K63" s="7" t="s">
         <v>19</v>
@@ -3511,7 +3545,7 @@
     </row>
     <row r="64" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B64" s="3">
         <v>2.1</v>
@@ -3520,25 +3554,25 @@
         <v>21</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F64" s="18" t="s">
-        <v>65</v>
+      <c r="F64" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="G64" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H64" s="14" t="s">
-        <v>40</v>
+      <c r="H64" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K64" s="7" t="s">
         <v>19</v>
@@ -3546,7 +3580,7 @@
     </row>
     <row r="65" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B65" s="3">
         <v>2.1</v>
@@ -3555,25 +3589,25 @@
         <v>21</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F65" s="18" t="s">
-        <v>65</v>
+      <c r="F65" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="G65" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H65" s="14" t="s">
-        <v>40</v>
+      <c r="H65" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K65" s="7" t="s">
         <v>19</v>
@@ -3581,7 +3615,7 @@
     </row>
     <row r="66" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B66" s="3">
         <v>2.1</v>
@@ -3590,25 +3624,25 @@
         <v>21</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F66" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H66" s="14" t="s">
-        <v>40</v>
+      <c r="F66" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K66" s="7" t="s">
         <v>19</v>
@@ -3616,34 +3650,34 @@
     </row>
     <row r="67" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B67" s="3">
         <v>2.1</v>
       </c>
       <c r="C67" s="3">
-        <v>21.1</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>49</v>
+        <v>21</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>198</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F67" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H67" s="14" t="s">
-        <v>40</v>
+      <c r="F67" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K67" s="7" t="s">
         <v>19</v>
@@ -3651,7 +3685,7 @@
     </row>
     <row r="68" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B68" s="3">
         <v>2.1</v>
@@ -3659,26 +3693,26 @@
       <c r="C68" s="3">
         <v>21.1</v>
       </c>
-      <c r="D68" s="16" t="s">
-        <v>49</v>
+      <c r="D68" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F68" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H68" s="14" t="s">
-        <v>40</v>
+      <c r="F68" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K68" s="7" t="s">
         <v>19</v>
@@ -3686,7 +3720,7 @@
     </row>
     <row r="69" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B69" s="3">
         <v>2.1</v>
@@ -3694,26 +3728,26 @@
       <c r="C69" s="3">
         <v>21.1</v>
       </c>
-      <c r="D69" s="16" t="s">
-        <v>49</v>
+      <c r="D69" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F69" s="19" t="s">
-        <v>69</v>
+      <c r="F69" s="18" t="s">
+        <v>64</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H69" s="14" t="s">
-        <v>40</v>
+      <c r="H69" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K69" s="7" t="s">
         <v>19</v>
@@ -3721,7 +3755,7 @@
     </row>
     <row r="70" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B70" s="3">
         <v>2.1</v>
@@ -3729,26 +3763,26 @@
       <c r="C70" s="3">
         <v>21.1</v>
       </c>
-      <c r="D70" s="16" t="s">
-        <v>49</v>
+      <c r="D70" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F70" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="14" t="s">
-        <v>40</v>
+      <c r="F70" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K70" s="7" t="s">
         <v>19</v>
@@ -3756,7 +3790,7 @@
     </row>
     <row r="71" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B71" s="3">
         <v>2.1</v>
@@ -3764,26 +3798,26 @@
       <c r="C71" s="3">
         <v>21.1</v>
       </c>
-      <c r="D71" s="16" t="s">
-        <v>49</v>
+      <c r="D71" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F71" s="13" t="s">
-        <v>39</v>
+      <c r="F71" s="18" t="s">
+        <v>64</v>
       </c>
       <c r="G71" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H71" s="14" t="s">
-        <v>40</v>
+      <c r="H71" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K71" s="7" t="s">
         <v>19</v>
@@ -3791,7 +3825,7 @@
     </row>
     <row r="72" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B72" s="3">
         <v>2.1</v>
@@ -3799,26 +3833,26 @@
       <c r="C72" s="3">
         <v>21.1</v>
       </c>
-      <c r="D72" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H72" s="14" t="s">
+      <c r="D72" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="J72" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K72" s="7" t="s">
         <v>19</v>
@@ -3826,7 +3860,7 @@
     </row>
     <row r="73" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B73" s="3">
         <v>2.1</v>
@@ -3834,26 +3868,26 @@
       <c r="C73" s="3">
         <v>21.1</v>
       </c>
-      <c r="D73" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F73" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H73" s="14" t="s">
-        <v>40</v>
+      <c r="D73" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>238</v>
+        <v>135</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K73" s="7" t="s">
         <v>19</v>
@@ -3861,7 +3895,7 @@
     </row>
     <row r="74" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B74" s="3">
         <v>2.1</v>
@@ -3869,32 +3903,67 @@
       <c r="C74" s="3">
         <v>21.1</v>
       </c>
-      <c r="D74" s="16" t="s">
-        <v>49</v>
+      <c r="D74" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F74" s="19" t="s">
-        <v>69</v>
+      <c r="F74" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H74" s="14" t="s">
-        <v>40</v>
+      <c r="H74" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K74" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B75" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="C75" s="3">
+        <v>21.1</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/tools/latest.xlsx
+++ b/tools/latest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10911"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B847370C-5158-0542-BDD4-965653AE9CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E26D21-8B95-B14D-B802-7E1B2D4E0996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🤩 public data release" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="234">
   <si>
     <t>Name</t>
   </si>
@@ -59,48 +59,45 @@
     <t/>
   </si>
   <si>
+    <t>Jen Zink</t>
+  </si>
+  <si>
+    <t>Lasso review and ensure WG knows</t>
+  </si>
+  <si>
+    <t>Physical Health</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Anthropometrics</t>
+  </si>
+  <si>
+    <t>Add sex-specific birth weight to `ph_ch_anthro` (see [Sex-Specific Birthweight for GA](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>ERICA derived fields for reliability and codes QC</t>
+  </si>
+  <si>
     <t>Santiago Torres Gomez</t>
   </si>
   <si>
-    <t>Dev Done</t>
-  </si>
-  <si>
-    <t>Physical Health</t>
-  </si>
-  <si>
-    <t>pending</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>Anthropometrics</t>
-  </si>
-  <si>
-    <t>Add sex-specific birth weight to `ph_ch_anthro` (see [Sex-Specific Birthweight for GA](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>ERICA derived fields for reliability and codes QC</t>
-  </si>
-  <si>
     <t>Not started yet</t>
   </si>
   <si>
     <t>Behavior &amp; Child-Caregiver Interaction</t>
   </si>
   <si>
-    <t>patch_pending</t>
-  </si>
-  <si>
     <t>ERICA</t>
   </si>
   <si>
-    <t>A future release will include reliability codes integrated into the primary coding dataset. Until then, users must perform this integration manually: see the ERICA Data Warning for instructions.</t>
-  </si>
-  <si>
     <t>Clean up crew: Multiple births</t>
   </si>
   <si>
@@ -113,631 +110,613 @@
     <t>Blank Fields for Siblings</t>
   </si>
   <si>
-    <t>Family-level (i.e., non-child-specific) instrument fields are currently populated only for the Main Child and not sibling records (e.g., HBCD Multiple Birth – Sibling). Until resolved, users should obtain family-level values for sibling participants by referencing the corresponding Main Child values (see mapping between Multibirth participants IDs in the [HBCD Private Release Notes](https://hbcd-docs-private.lassoinformatics.com/#download)).</t>
+    <t>Family-level (i.e., non-child-specific) instrument fields are currently populated only for the Main Child, not sibling records (e.g., HBCD Multiple Birth – Sibling). Until resolved, users should obtain family-level values for sibling participants from the corresponding Main Child record. See the participant ID mapping in the [HBCD Private Release Notes](https://hbcd-docs-private.lassoinformatics.com/#download).</t>
   </si>
   <si>
     <t>[DATA ERROR]- FAD scoring issues at V06</t>
   </si>
   <si>
+    <t>known_issue</t>
+  </si>
+  <si>
+    <t>FAD</t>
+  </si>
+  <si>
+    <t>N=4 V06 participants with &lt;3 item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- MAPTSTL scores incorrectly marked as "not enough answers to compute score"</t>
+  </si>
+  <si>
+    <t>MAPS-TL (Tod)</t>
+  </si>
+  <si>
+    <t>Pro-rated scoring for `mh_cg_mapdb__tod` not yet implemented; N=16 participants missing scores.</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST] - static and dynamic tables</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>Static &amp; Dynamic Tables</t>
+  </si>
+  <si>
+    <t>The Demographics domain includes 2 tables with derived information grouped into visit-specific data ([Visit Info](https://docs.hbcdstudy.org/latest/instruments/demo/visitinfo/)) and general demographics ([Basic Demographics](https://docs.hbcdstudy.org/latest/instruments/demo/basicdemo/)). In a future release, these tables will be restructured to instead organize variables as either longitudinal (dynamic measures that change over time) or global (static measures, such as sex assigned at birth and race/ethnicity).</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- ecPROMIS child-caregiver infant</t>
+  </si>
+  <si>
+    <t>ecPROMIS CC</t>
+  </si>
+  <si>
+    <t>N=12 V03 participants with &lt;3 item responses are incorrectly scored as `0` in `mh_cg_pms__cc__inf`; set values to null prior to analysis.</t>
+  </si>
+  <si>
+    <t>[IMAGING] Add Cook's distance to tabulated imaging data</t>
+  </si>
+  <si>
+    <t>MRI</t>
+  </si>
+  <si>
+    <t>Cook's Distance</t>
+  </si>
+  <si>
+    <t>Addition Cook's distance values computed for fMRI.</t>
+  </si>
+  <si>
+    <t>[2.0 SCORING CORRECTION NEEDED]- V03 MAPS-TL</t>
+  </si>
+  <si>
+    <t>MAPS-TL (&lt;1yr)</t>
+  </si>
+  <si>
+    <t>N=4 participants with no item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- implausible gestational ages in multiple instruments (parameter-based filtering)</t>
+  </si>
+  <si>
+    <t>Santiago Torres Gomez, Stephanie Averill</t>
+  </si>
+  <si>
     <t>Active</t>
   </si>
   <si>
-    <t>known_issue</t>
-  </si>
-  <si>
-    <t>FAD</t>
-  </si>
-  <si>
-    <t>N=4 V06 participants with &lt;3 item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- MAPTSTL scores incorrectly marked as "not enough answers to compute score"</t>
-  </si>
-  <si>
-    <t>Jen Zink</t>
-  </si>
-  <si>
-    <t>Lasso review and ensure WG knows</t>
-  </si>
-  <si>
-    <t>MAPS-TL (Tod)</t>
-  </si>
-  <si>
-    <t>Pro-rated scoring for `mh_cg_mapdb__tod` not yet implemented; N=16 participants missing scores.</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST] - static and dynamic tables</t>
-  </si>
-  <si>
-    <t>Demographics</t>
-  </si>
-  <si>
-    <t>Static &amp; Dynamic Tables</t>
-  </si>
-  <si>
-    <t>The Demographics domain includes 2 tables with derived information grouped into visit-specific data ([Visit Info](https://docs.hbcdstudy.org/latest/instruments/demo/visitinfo/)) and general demographics ([Basic Demographics](https://docs.hbcdstudy.org/latest/instruments/demo/basicdemo/)). In a future release, these tables will be restructured to instead organize variables as either longitudinal (dynamic measures that change over time) or global (static measures, such as sex assigned at birth and race/ethnicity).</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- ecPROMIS child-caregiver infant</t>
-  </si>
-  <si>
-    <t>ecPROMIS CC</t>
-  </si>
-  <si>
-    <t>N=12 V03 participants with &lt;3 item responses are incorrectly scored as `0` in `mh_cg_pms__cc__inf`; set values to null prior to analysis.</t>
-  </si>
-  <si>
-    <t>[IMAGING] Add Cook's distance to tabulated imaging data</t>
-  </si>
-  <si>
-    <t>Eric Feczko</t>
-  </si>
-  <si>
-    <t>MRI</t>
-  </si>
-  <si>
-    <t>Cook's Distance</t>
-  </si>
-  <si>
-    <t>Addition Cook's distance values computed for fMRI.</t>
-  </si>
-  <si>
-    <t>[2.0 SCORING CORRECTION NEEDED]- V03 MAPS-TL</t>
+    <t>Implausible GA</t>
+  </si>
+  <si>
+    <t>A small subset of participants have implausible `gestational_age` (V01 only) values  for one or more instrument. Until corrected, review GA distribution to exclude outliers from analysis (should be positive and generally &lt; 45 weeks).</t>
+  </si>
+  <si>
+    <t>[LORIS BUG]- adjusted age</t>
+  </si>
+  <si>
+    <t>Adjusted age contains N=303 "unknown missing" values that are also missing 'Date of Administration'.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- MAV01 in Release 2.0</t>
+  </si>
+  <si>
+    <t>Basic Demo</t>
+  </si>
+  <si>
+    <t>N=14 participants in `sed_basic_demographics` have a Maternal Age at V01 of 0; exclude these values from analyses until corrected.</t>
+  </si>
+  <si>
+    <t>[DD ERROR] - push text in score fields to 'notes' fields (SPM2 &amp; ecPROMIS-PAGS)</t>
+  </si>
+  <si>
+    <t>Score text</t>
+  </si>
+  <si>
+    <t>Text inappropriately located in score fields where score is missing to be moved to corresponding 'notes' field (impacts ecPROMIS-PAGS; MAPS-TL; SPM-2).</t>
+  </si>
+  <si>
+    <t>TLFB not parsed items</t>
+  </si>
+  <si>
+    <t>TLFB</t>
+  </si>
+  <si>
+    <t>PNR data were incorrectly reported using TLFB versions 1/2 and will be updated to [version 3 specific to PNR](https://docs.hbcdstudy.org/latest/instruments/pregexp/su/tlfb/#v3)</t>
+  </si>
+  <si>
+    <t>All decline to answer will still report as zero - eHITS</t>
+  </si>
+  <si>
+    <t>Social &amp; Environmental Determinants</t>
+  </si>
+  <si>
+    <t>eHITS</t>
+  </si>
+  <si>
+    <t>Participants missing all item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
+  </si>
+  <si>
+    <t>[POSSIBLE DATA ERROR] - empty columns in preg meds file</t>
+  </si>
+  <si>
+    <t>Pregnancy &amp; Environmental Exposure</t>
+  </si>
+  <si>
+    <t>data_warning</t>
+  </si>
+  <si>
+    <t>On hold- need more info</t>
+  </si>
+  <si>
+    <t>HealthV1-Meds</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>[TYPE_DATA INCORRECT] - ph_ch_anthro_average_bmi</t>
+  </si>
+  <si>
+    <t>The data dictionary element `type_data` for `average_bmi` will be corrected to `double` (currently=`character`).</t>
+  </si>
+  <si>
+    <t>[DD+DATA ERROR] Nail type field added for 2.0 all "Unknown"</t>
+  </si>
+  <si>
+    <t>Biospecimens &amp; Omics</t>
+  </si>
+  <si>
+    <t>Nails</t>
+  </si>
+  <si>
+    <t>Nail type is `4` (Unknown) in the main results table (`*_nails_results`) and should be obtained from the specimen table (`*_nails_type`).</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]- consistent ICD code names</t>
+  </si>
+  <si>
+    <t>PEX Health</t>
+  </si>
+  <si>
+    <t>ICD codes for the `pex_bm_health*`  tables are inconsistently provided, sometimes missing corresponding names/labels. For example, medication names are present for the _Health V1- Medications_, while the _Health V2- Pregnancy_ instrument only has medication codes without corresponding labels. Until resolved, users can use external packages to merge ICD labels if needed: [Stata](https://www.stata.com/features/overview/icd/), [SAS](https://hcup-us.ahrq.gov/toolssoftware/ccsr/dxccsr.jsp), [R](https://www.rdocumentation.org/packages/icd/versions/3.3)</t>
+  </si>
+  <si>
+    <t>Inclusion of Blood Spot Card Results data from USDTL. Addressing issue of incorrect cleaning practices at sites that affect test results PEth.</t>
+  </si>
+  <si>
+    <t>Blood</t>
+  </si>
+  <si>
+    <t>Inclusion of Blood Spot Card Results data from USDTL.</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST] ERICA - add age &amp; date_taken fields back to ERICA once corrected (post 2.1 patch)</t>
+  </si>
+  <si>
+    <t>Add all age and `date_taken` fields (currently excluded due to use of coding rather than visit dates).</t>
+  </si>
+  <si>
+    <t>[SCORING CORRECTION NEEDED]- EPDS</t>
+  </si>
+  <si>
+    <t>EPDS</t>
+  </si>
+  <si>
+    <t>Inconsistent scoring: (1) item responses present, but score is null (N=1); (2) all items null, but score is `0` (N≥3).</t>
+  </si>
+  <si>
+    <t>Anthro: ph_ch_anthro_head_for_age_boys_z_score</t>
+  </si>
+  <si>
+    <t>Growth (`ph_ch_anthro`) filter ranges will be updated to be visit-specific, as current ranges allow biologically implausible values (see [Range Checks](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]-household roster - sex variable</t>
+  </si>
+  <si>
+    <t>Demo</t>
+  </si>
+  <si>
+    <t>Add household roster fields capturing the sex of listed individuals (adult &amp; child tables).</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]- anthro z-score calcs when no EDD/adjusted age available</t>
+  </si>
+  <si>
+    <t>on hold/later</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>[POSSIBLE DATA ERROR]- relationship status at V03</t>
+  </si>
+  <si>
+    <t>Relationship status was inappropriately collected at V02/V03 for all cohorts and should have been restricted to cases where there was a change in caregiver (i.e. only Alternative Caregiver cohorts should have this field populated). Data for non-ACG cohorts to be excluded.</t>
+  </si>
+  <si>
+    <t>Bayley invalid subscores (-9999) (parameter-based filtering)</t>
+  </si>
+  <si>
+    <t>Neurocognition &amp; Language</t>
+  </si>
+  <si>
+    <t>Bayley</t>
+  </si>
+  <si>
+    <t>Remove invalid scores of `-9999`; until resolved, users should remove this participant data prior to analysis.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]- age fields tied to visit start date</t>
+  </si>
+  <si>
+    <t>Santiago Torres Gomez, laetitia.fesselier@mcin.ca</t>
+  </si>
+  <si>
+    <t>EEG</t>
+  </si>
+  <si>
+    <t>Age fields</t>
+  </si>
+  <si>
+    <t>Chronological and adjusted age fall outside of 3-9 months in N=74 V03 sessions (site entry errors); exclude age values prior to analysis.</t>
+  </si>
+  <si>
+    <t>[POSSIBLE DATA ERROR]- roster at V02 or V03 (parameter-based filtering is precursor)</t>
+  </si>
+  <si>
+    <t>Roster was inappropriately collected at V02/V03 for all cohorts and should have been restricted to V02 PNRs and alternate caregiver cohorts; to be excluded.</t>
+  </si>
+  <si>
+    <t>Child Nutrition Questionnaire</t>
+  </si>
+  <si>
+    <t>Child Nutrition</t>
+  </si>
+  <si>
+    <t>Addition of the Child Nutrition Questionnaire.</t>
+  </si>
+  <si>
+    <t>Deferred Imitation Task: Gong and Berry-Go-Round</t>
+  </si>
+  <si>
+    <t>Deferred Imitation</t>
+  </si>
+  <si>
+    <t>Addition of instrument: Deferred Imitation Task: Gong and Berry-Go-Round</t>
+  </si>
+  <si>
+    <t>Demographics V6 Adult</t>
+  </si>
+  <si>
+    <t>Addition of V6 Adult</t>
+  </si>
+  <si>
+    <t>Demographics V6 Child</t>
+  </si>
+  <si>
+    <t>Addition of V6 Child</t>
+  </si>
+  <si>
+    <t>Geocoded Linkage from Home and Work Addresses</t>
+  </si>
+  <si>
+    <t>Matthew Schmidt</t>
+  </si>
+  <si>
+    <t>ETL to review</t>
+  </si>
+  <si>
+    <t>GLED</t>
+  </si>
+  <si>
+    <t>Addition of Geocoded Linkage from Home and Work Addresses</t>
+  </si>
+  <si>
+    <t>Incarceration Questionnaire</t>
+  </si>
+  <si>
+    <t>Incarceration</t>
+  </si>
+  <si>
+    <t>Addition of the Incarceration Questionnaire</t>
+  </si>
+  <si>
+    <t>MacArthur-Bates CDI-2 Language</t>
+  </si>
+  <si>
+    <t>CDI-2</t>
+  </si>
+  <si>
+    <t>Addition of the MacArthur-Bates CDI-2 Language</t>
+  </si>
+  <si>
+    <t>MAPS-EASI- Toddler</t>
+  </si>
+  <si>
+    <t>MAPS-EASI</t>
+  </si>
+  <si>
+    <t>Addition of the MAPS-EASI- Toddler</t>
+  </si>
+  <si>
+    <t>Medical History V1 (new at V04/V06)</t>
+  </si>
+  <si>
+    <t>Med History V1</t>
+  </si>
+  <si>
+    <t>Addition of V06</t>
+  </si>
+  <si>
+    <t>Modified Checklist for Autism in Toddlers (MCHAT)</t>
+  </si>
+  <si>
+    <t>MCHAT</t>
+  </si>
+  <si>
+    <t>Addition of the Modified Checklist for Autism in Toddlers</t>
+  </si>
+  <si>
+    <t>PEDsQL</t>
+  </si>
+  <si>
+    <t>Addition of the PEDsQL</t>
+  </si>
+  <si>
+    <t>Transition in Care Questionnaire</t>
+  </si>
+  <si>
+    <t>Tim Meyer, Stephanie Averill, regis.ongaro-carcy@mcin.ca</t>
+  </si>
+  <si>
+    <t>TIC Questionnaire</t>
+  </si>
+  <si>
+    <t>Addition of TIC Questionnaire table</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]- add in LORIS imaging form variables, MRI checklist summary forms</t>
+  </si>
+  <si>
+    <t>Archived to BR</t>
+  </si>
+  <si>
+    <t>Summary Forms</t>
+  </si>
+  <si>
+    <t>Add MRI Scan Session + Data Summary Forms (information from the MRI technician obtained on day of scan).</t>
+  </si>
+  <si>
+    <t>[DATA ISSUE] - cdiwgen values over 100</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>Percentiles incorrectly converted for N=36 cases, resulting in values &gt;100 ('Adjusted Percentile' incorrectly parsed from 'Total Produced' instead of 'Total Produced Percentile-sex (adjusted)')</t>
+  </si>
+  <si>
+    <t>Participant status and withdrawal field harmonization</t>
+  </si>
+  <si>
+    <t>Dan Duhon, Matthew Schmidt</t>
+  </si>
+  <si>
+    <t>Visit Info</t>
+  </si>
+  <si>
+    <t>Harmonize participant status and withdrawal fields</t>
+  </si>
+  <si>
+    <t>[DATA ISSUE] - VABS reasons for missingness are wrong</t>
+  </si>
+  <si>
+    <t>LORIS review</t>
+  </si>
+  <si>
+    <t>Vineland</t>
+  </si>
+  <si>
+    <t>The Coping Skills, Domestic, and Written subscales are not administered at V05 because children are too young. However, for some participants, the missing reason is incorrectly coded as "Logic skipped" or "Unknown" in the shadow matrix. In addition, the age of one child is outside of the valid bounds for V05.</t>
+  </si>
+  <si>
+    <t>[DATA ISSUE]- Screen_mother_race_multi  majority are 0</t>
+  </si>
+  <si>
+    <t>The `screen_race_multi__*` variables are almost entirely coded as '0' and should not be used for analysis. Users interested in race and ethnicity information should instead use the corresponding derived ACS race and ethnicity variable. Values will be corrected in a future release.</t>
+  </si>
+  <si>
+    <t>[TEMP ITEM] update JSON metadata to match Lasso/DEAP updates</t>
+  </si>
+  <si>
+    <t>UNSURE</t>
+  </si>
+  <si>
+    <t>unsure</t>
+  </si>
+  <si>
+    <t>Cleanup crew: Inclusion of family pregnancy ID</t>
+  </si>
+  <si>
+    <t>Dan Duhon</t>
+  </si>
+  <si>
+    <t>FamilyID</t>
+  </si>
+  <si>
+    <t>A `FamilyID` field will be added to instruments to identify sibling relationships. Until then, sibling ID mapping (Main Child vs Sibling) is provided in the [HBCD Private Release Notes](https://hbcd-docs-private.lassoinformatics.com/#download).</t>
+  </si>
+  <si>
+    <t>VABS age out of window</t>
+  </si>
+  <si>
+    <t>[DATA REQUEST]- revise formatting of vision screener files</t>
+  </si>
+  <si>
+    <t>Vision Screener</t>
+  </si>
+  <si>
+    <t>Add more fields to `ph_ch_vs` (current release only includes completion status and overall screening results).</t>
+  </si>
+  <si>
+    <t>Remove 'sequence' field from all tables in Lasso</t>
+  </si>
+  <si>
+    <t>Sequence Field</t>
+  </si>
+  <si>
+    <t>The currently included Sequence field is blank across all instruments and will be removed.</t>
+  </si>
+  <si>
+    <t>[DATA ERROR]-MLDS  total hours per week of non-parental hours</t>
+  </si>
+  <si>
+    <t>MLDS</t>
+  </si>
+  <si>
+    <t>Total non-parental hours/week (`ncl_ch_mlds_arr_hr_wk`) includes implausible values due to data entry errors. Exclude values &gt;168 hours from analysis.</t>
+  </si>
+  <si>
+    <t>Instruction metadata extraction from REDCap DD</t>
+  </si>
+  <si>
+    <t>Instruction</t>
+  </si>
+  <si>
+    <t>Instruction text in each form's metadata is automatically extracted from the most recent `instruction` field in the REDCap Data Dictionary (based on field order). Because this process is automated, it may produce the following issues: (1) If an instruction spans multiple fields, only the last portion will be captured and/or (2) Some fields may display text intended for a previous section. Until this is corrected, please refer to original forms for accurate instruction text.</t>
+  </si>
+  <si>
+    <t>BIDs run label not in chronological order</t>
+  </si>
+  <si>
+    <t>Cecile Madjar</t>
+  </si>
+  <si>
+    <t>Run ID</t>
+  </si>
+  <si>
+    <t>The `run-{X}` field may not reflect chronological acquisition order. While this affects both **raw BIDS and derivatives**, data remain internally consistent (i.e. run IDs match between raw and processed datasets).</t>
+  </si>
+  <si>
+    <t>BISQR: infant sleep score - need to add</t>
   </si>
   <si>
     <t>Waiting on WG feedback</t>
   </si>
   <si>
-    <t>MAPS-TL (&lt;1yr)</t>
-  </si>
-  <si>
-    <t>N=4 participants with no item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- implausible gestational ages in multiple instruments (parameter-based filtering)</t>
-  </si>
-  <si>
-    <t>Santiago Torres Gomez, Stephanie Averill</t>
-  </si>
-  <si>
-    <t>Implausible GA</t>
-  </si>
-  <si>
-    <t>A small subset of participants have implausible `gestational_age` (V01 only) values  for one or more instrument. Until corrected, review GA distribution to exclude outliers from analysis (should be positive and generally &lt; 45 weeks).</t>
-  </si>
-  <si>
-    <t>[LORIS BUG]- adjusted age</t>
-  </si>
-  <si>
-    <t>Adjusted age contains N=303 "unknown missing" values that are also missing 'Date of Administration'.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- MAV01 in Release 2.0</t>
-  </si>
-  <si>
-    <t>Basic Demo</t>
-  </si>
-  <si>
-    <t>N=14 participants in `sed_basic_demographics` have a Maternal Age at V01 of 0; exclude these values from analyses until corrected.</t>
-  </si>
-  <si>
-    <t>[DD ERROR] - push text in score fields to 'notes' fields (SPM2 &amp; ecPROMIS-PAGS)</t>
-  </si>
-  <si>
-    <t>patch_known_issue</t>
-  </si>
-  <si>
-    <t>Score text</t>
-  </si>
-  <si>
-    <t>Text inappropriately located in score fields where score is missing to be moved to corresponding 'notes' field (impacts ecPROMIS-PAGS; MAPS-TL; SPM-2).</t>
-  </si>
-  <si>
-    <t>TLFB not parsed items</t>
-  </si>
-  <si>
-    <t>TLFB</t>
-  </si>
-  <si>
-    <t>PNR data were incorrectly reported using TLFB versions 1/2 and will be updated to [version 3 specific to PNR](https://docs.hbcdstudy.org/latest/instruments/pregexp/su/tlfb/#v3)</t>
-  </si>
-  <si>
-    <t>All decline to answer will still report as zero - eHITS</t>
-  </si>
-  <si>
-    <t>Social &amp; Environmental Determinants</t>
-  </si>
-  <si>
-    <t>eHITS</t>
-  </si>
-  <si>
-    <t>Participants missing all item responses are incorrectly scored as `0`; set values to null prior to analysis.</t>
-  </si>
-  <si>
-    <t>[POSSIBLE DATA ERROR] - empty columns in preg meds file</t>
-  </si>
-  <si>
-    <t>Pregnancy &amp; Environmental Exposure</t>
-  </si>
-  <si>
-    <t>data_warning</t>
-  </si>
-  <si>
-    <t>On hold- need more info</t>
-  </si>
-  <si>
-    <t>HealthV1-Meds</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>[TYPE_DATA INCORRECT] - ph_ch_anthro_average_bmi</t>
-  </si>
-  <si>
-    <t>The data dictionary element `type_data` for `average_bmi` will be corrected to `double` (currently=`character`).</t>
+    <t>BISQ-SF</t>
+  </si>
+  <si>
+    <t>Add Infant Sleep (IS) sub-scale score to `ph_cg_bisq`.</t>
+  </si>
+  <si>
+    <t>pex_bm_healthv2_preg__exp__pnv_007__01 is completely blank</t>
+  </si>
+  <si>
+    <t>Stephanie Averill</t>
+  </si>
+  <si>
+    <t>Ongoing</t>
+  </si>
+  <si>
+    <t>Healthv2 Preg</t>
+  </si>
+  <si>
+    <t>The field for the date when PNV was stopped (`pex_bm_healthv2_preg__exp__pnv_007__01`) is blank, despite participants having reported stopping.</t>
+  </si>
+  <si>
+    <t>aspirin items in health v2 preg</t>
+  </si>
+  <si>
+    <t>Note that items about aspirin use (`pex_bm_healthv2_preg__exp__pnv_{011|012}`) are largely blank.</t>
+  </si>
+  <si>
+    <t>MRI Derivatives - QSIprep - Generate tabular data for QSIRECON</t>
+  </si>
+  <si>
+    <t>QSIRecon</t>
+  </si>
+  <si>
+    <t>Tabulated data for QSIRecon (participant data combined across derivative files into single tidy table) will be provided in a future release.</t>
+  </si>
+  <si>
+    <t>DD 'instruction' field all blank</t>
+  </si>
+  <si>
+    <t>The 'instruction' data dictionary element is currently blank.</t>
+  </si>
+  <si>
+    <t>8 PNR not administered V1 portion of TLFB</t>
+  </si>
+  <si>
+    <t>Stephanie Averill, Santiago Torres Gomez</t>
+  </si>
+  <si>
+    <t>Select participants (N=8) were recruited postnatally, but not administered the V1 portion of the TLFB. When this was recognized, the participants were administered the TLFB at the next in-person visit, resulting in a longer recall period than specified in the protocol.</t>
+  </si>
+  <si>
+    <t>Early Child Care and Education</t>
+  </si>
+  <si>
+    <t>regis.ongaro-carcy@mcin.ca</t>
+  </si>
+  <si>
+    <t>ECHO</t>
+  </si>
+  <si>
+    <t>Addition of the Early Child Care and Education</t>
+  </si>
+  <si>
+    <t>Addition of date to OSPREY pipeline time string</t>
+  </si>
+  <si>
+    <t>fMRI V08 video task processing pipeline</t>
+  </si>
+  <si>
+    <t>New; needs discussion</t>
+  </si>
+  <si>
+    <t>fMRI video task consistency</t>
+  </si>
+  <si>
+    <t>SSL based QALAS pipeline</t>
+  </si>
+  <si>
+    <t>Gabi raw BIDs</t>
+  </si>
+  <si>
+    <t>Cecile Madjar, Harshitha Anuganti, Jesse Erdmann</t>
+  </si>
+  <si>
+    <t>Novel Tech &amp; Wearable Sensors</t>
+  </si>
+  <si>
+    <t>GABI</t>
+  </si>
+  <si>
+    <t>Addition of raw BIDS data for GABI (infant heart rate).</t>
+  </si>
+  <si>
+    <t>MADE v1.7.0</t>
+  </si>
+  <si>
+    <t>Tanya Pandhi</t>
+  </si>
+  <si>
+    <t>HBCD-MADE derivatives processed through updated version v1.7.0</t>
   </si>
   <si>
     <t>Add DICOMs to release</t>
   </si>
   <si>
-    <t>Tanya Pandhi</t>
-  </si>
-  <si>
     <t>Source DICOMs</t>
   </si>
   <si>
     <t>Add source DICOMs for all imaging modalities.</t>
   </si>
   <si>
-    <t>[DD+DATA ERROR] Nail type field added for 2.0 all "Unknown"</t>
-  </si>
-  <si>
-    <t>Biospecimens &amp; Omics</t>
-  </si>
-  <si>
-    <t>Nails</t>
-  </si>
-  <si>
-    <t>Nail type is `4` (Unknown) in the main results table (`*_nails_results`) and should be obtained from the specimen table (`*_nails_type`).</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- consistent ICD code names</t>
-  </si>
-  <si>
-    <t>PEX Health</t>
-  </si>
-  <si>
-    <t>ICD codes for the `pex_bm_health*`  tables are inconsistently provided, sometimes missing corresponding names/labels. For example, medication names are present for the _Health V1- Medications_, while the _Health V2- Pregnancy_ instrument only has medication codes without corresponding labels. Until resolved, users can use external packages to merge ICD labels if needed: [Stata](https://www.stata.com/features/overview/icd/), [SAS](https://hcup-us.ahrq.gov/toolssoftware/ccsr/dxccsr.jsp), [R](https://www.rdocumentation.org/packages/icd/versions/3.3)</t>
-  </si>
-  <si>
-    <t>Inclusion of Blood Spot Card Results data from USDTL. Addressing issue of incorrect cleaning practices at sites that affect test results PEth.</t>
-  </si>
-  <si>
-    <t>Blood</t>
-  </si>
-  <si>
-    <t>Inclusion of Blood Spot Card Results data from USDTL.</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST] ERICA - add age &amp; date_taken fields back to ERICA once corrected (post 2.1 patch)</t>
-  </si>
-  <si>
-    <t>Add all age and `date_taken` fields (currently excluded due to use of coding rather than visit dates).</t>
-  </si>
-  <si>
-    <t>[SCORING CORRECTION NEEDED]- EPDS</t>
-  </si>
-  <si>
-    <t>LORIS review</t>
-  </si>
-  <si>
-    <t>EPDS</t>
-  </si>
-  <si>
-    <t>Inconsistent scoring: (1) item responses present, but score is null (N=1); (2) all items null, but score is `0` (N≥3).</t>
-  </si>
-  <si>
-    <t>Anthro: ph_ch_anthro_head_for_age_boys_z_score</t>
-  </si>
-  <si>
-    <t>Growth (`ph_ch_anthro`) filter ranges will be updated to be visit-specific, as current ranges allow biologically implausible values (see [Range Checks](https://docs.hbcdstudy.org/latest/instruments/physhealth/growth/#warning)).</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]-household roster - sex variable</t>
-  </si>
-  <si>
-    <t>Demo</t>
-  </si>
-  <si>
-    <t>Add household roster fields capturing the sex of listed individuals (adult &amp; child tables).</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- anthro z-score calcs when no EDD/adjusted age available</t>
-  </si>
-  <si>
-    <t>on hold/later</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>[POSSIBLE DATA ERROR]- relationship status at V03</t>
-  </si>
-  <si>
-    <t>Relationship status was inappropriately collected at V02/V03 for all cohorts and should have been restricted to cases where there was a change in caregiver (i.e. only Alternative Caregiver cohorts should have this field populated). Data for non-ACG cohorts to be excluded.</t>
-  </si>
-  <si>
-    <t>Bayley invalid subscores (-9999) (parameter-based filtering)</t>
-  </si>
-  <si>
-    <t>Neurocognition &amp; Language</t>
-  </si>
-  <si>
-    <t>Bayley</t>
-  </si>
-  <si>
-    <t>Remove invalid scores of `-9999`; until resolved, users should remove this participant data prior to analysis.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- age fields tied to visit start date</t>
-  </si>
-  <si>
-    <t>Santiago Torres Gomez, laetitia.fesselier@mcin.ca</t>
-  </si>
-  <si>
-    <t>EEG</t>
-  </si>
-  <si>
-    <t>Age fields</t>
-  </si>
-  <si>
-    <t>Chronological and adjusted age fall outside of 3-9 months in N=74 V03 sessions (site entry errors); exclude age values prior to analysis.</t>
-  </si>
-  <si>
-    <t>Gabi raw BIDs</t>
-  </si>
-  <si>
-    <t>Cecile Madjar, Harshitha Anuganti, Jesse Erdmann</t>
-  </si>
-  <si>
-    <t>Deployed in LORIS</t>
-  </si>
-  <si>
-    <t>Novel Tech &amp; Wearable Sensors</t>
-  </si>
-  <si>
-    <t>GABI</t>
-  </si>
-  <si>
-    <t>Addition of raw BIDS data for GABI (infant heart rate).</t>
-  </si>
-  <si>
-    <t>[POSSIBLE DATA ERROR]- roster at V02 or V03 (parameter-based filtering is precursor)</t>
-  </si>
-  <si>
-    <t>Roster was inappropriately collected at V02/V03 for all cohorts and should have been restricted to V02 PNRs and alternate caregiver cohorts; to be excluded.</t>
-  </si>
-  <si>
-    <t>Child Nutrition Questionnaire</t>
-  </si>
-  <si>
-    <t>regis.ongaro-carcy@mcin.ca</t>
-  </si>
-  <si>
-    <t>Child Nutrition</t>
-  </si>
-  <si>
-    <t>Addition of the Child Nutrition Questionnaire.</t>
-  </si>
-  <si>
-    <t>Deferred Imitation Task: Gong and Berry-Go-Round</t>
-  </si>
-  <si>
-    <t>Deferred Imitation</t>
-  </si>
-  <si>
-    <t>Addition of instrument: Deferred Imitation Task: Gong and Berry-Go-Round</t>
-  </si>
-  <si>
-    <t>Demographics V6 Adult</t>
-  </si>
-  <si>
-    <t>Addition of V6 Adult</t>
-  </si>
-  <si>
-    <t>Demographics V6 Child</t>
-  </si>
-  <si>
-    <t>Addition of V6 Child</t>
-  </si>
-  <si>
-    <t>Geocoded Linkage from Home and Work Addresses</t>
-  </si>
-  <si>
-    <t>Matthew Schmidt, regis.ongaro-carcy@mcin.ca</t>
-  </si>
-  <si>
-    <t>GLED</t>
-  </si>
-  <si>
-    <t>Addition of Geocoded Linkage from Home and Work Addresses</t>
-  </si>
-  <si>
-    <t>Incarceration Questionnaire</t>
-  </si>
-  <si>
-    <t>Incarceration</t>
-  </si>
-  <si>
-    <t>Addition of the Incarceration Questionnaire</t>
-  </si>
-  <si>
-    <t>MacArthur-Bates CDI-2 Language</t>
-  </si>
-  <si>
-    <t>CDI-2</t>
-  </si>
-  <si>
-    <t>Addition of the MacArthur-Bates CDI-2 Language</t>
-  </si>
-  <si>
-    <t>MAPS-EASI- Toddler</t>
-  </si>
-  <si>
-    <t>MAPS-EASI</t>
-  </si>
-  <si>
-    <t>Addition of the MAPS-EASI- Toddler</t>
-  </si>
-  <si>
-    <t>Medical History V1 (new at V04/V06)</t>
-  </si>
-  <si>
-    <t>Med History V1</t>
-  </si>
-  <si>
-    <t>Addition of V06</t>
-  </si>
-  <si>
-    <t>Modified Checklist for Autism in Toddlers (MCHAT)</t>
-  </si>
-  <si>
-    <t>MCHAT</t>
-  </si>
-  <si>
-    <t>Addition of the Modified Checklist for Autism in Toddlers</t>
-  </si>
-  <si>
-    <t>PEDsQL</t>
-  </si>
-  <si>
-    <t>Addition of the PEDsQL</t>
-  </si>
-  <si>
-    <t>Transition in Care Questionnaire</t>
-  </si>
-  <si>
-    <t>Tim Meyer, Stephanie Averill, regis.ongaro-carcy@mcin.ca</t>
-  </si>
-  <si>
-    <t>TIC Questionnaire</t>
-  </si>
-  <si>
-    <t>Addition of TIC Questionnaire table</t>
-  </si>
-  <si>
-    <t>MADE v1.7.0</t>
-  </si>
-  <si>
-    <t>HBCD-MADE derivatives processed through updated version v1.7.0</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- add in LORIS imaging form variables, MRI checklist summary forms</t>
-  </si>
-  <si>
-    <t>Archived to BR</t>
-  </si>
-  <si>
-    <t>Summary Forms</t>
-  </si>
-  <si>
-    <t>Add MRI Scan Session + Data Summary Forms (information from the MRI technician obtained on day of scan).</t>
-  </si>
-  <si>
-    <t>[REMOVE FIELDS]- ERICA locomotor ability fields</t>
-  </si>
-  <si>
-    <t>Remove `locomotor_ability` fields from both tables</t>
-  </si>
-  <si>
-    <t>[DATA ISSUE] - cdiwgen values over 100</t>
-  </si>
-  <si>
-    <t>CDI</t>
-  </si>
-  <si>
-    <t>Percentiles incorrectly converted for N=36 cases, resulting in values &gt;100 ('Adjusted Percentile' incorrectly parsed from 'Total Produced' instead of 'Total Produced Percentile-sex (adjusted)')</t>
-  </si>
-  <si>
-    <t>Participant status and withdrawal field harmonization</t>
-  </si>
-  <si>
-    <t>Dan Duhon, Matthew Schmidt</t>
-  </si>
-  <si>
-    <t>ETL to review</t>
-  </si>
-  <si>
-    <t>Visit Info</t>
-  </si>
-  <si>
-    <t>Harmonize participant status and withdrawal fields</t>
-  </si>
-  <si>
-    <t>[DATA ISSUE] - VABS reasons for missingness are wrong</t>
-  </si>
-  <si>
-    <t>Vineland</t>
-  </si>
-  <si>
-    <t>The Coping Skills, Domestic, and Written subscales are not administered at V05 because children are too young. However, for some participants, the missing reason is incorrectly coded as "Logic skipped" or "Unknown" in the shadow matrix. In addition, the age of one child is outside of the valid bounds for V05.</t>
-  </si>
-  <si>
-    <t>[DATA ISSUE]- Screen_mother_race_multi  majority are 0</t>
-  </si>
-  <si>
-    <t>The `screen_race_multi__*` variables are almost entirely coded as '0' and should not be used for analysis. Users interested in race and ethnicity information should instead use the corresponding derived ACS race and ethnicity variable. Values will be corrected in a future release.</t>
-  </si>
-  <si>
-    <t>[TEMP ITEM] update JSON metadata to match Lasso/DEAP updates</t>
-  </si>
-  <si>
-    <t>New; needs discussion</t>
-  </si>
-  <si>
-    <t>UNSURE</t>
-  </si>
-  <si>
-    <t>unsure</t>
-  </si>
-  <si>
-    <t>Cleanup crew: Inclusion of family pregnancy ID</t>
-  </si>
-  <si>
-    <t>Dan Duhon</t>
-  </si>
-  <si>
-    <t>FamilyID</t>
-  </si>
-  <si>
-    <t>A `FamilyID` field will be added to instruments to identify sibling relationships. Until then, sibling ID mapping (Main Child vs Sibling) is provided in the [HBCD Private Release Notes](https://hbcd-docs-private.lassoinformatics.com/#download).</t>
-  </si>
-  <si>
-    <t>VABS age out of window</t>
-  </si>
-  <si>
-    <t>[DATA REQUEST]- revise formatting of vision screener files</t>
-  </si>
-  <si>
-    <t>Vision Screener</t>
-  </si>
-  <si>
-    <t>Add more fields to `ph_ch_vs` (current release only includes completion status and overall screening results).</t>
-  </si>
-  <si>
-    <t>Remove 'sequence' field from all tables in Lasso</t>
-  </si>
-  <si>
-    <t>Sequence Field</t>
-  </si>
-  <si>
-    <t>The currently included Sequence field is blank across all instruments and will be removed.</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]-MLDS  total hours per week of non-parental hours</t>
-  </si>
-  <si>
-    <t>MLDS</t>
-  </si>
-  <si>
-    <t>Total non-parental hours/week (`ncl_ch_mlds_arr_hr_wk`) includes implausible values due to data entry errors. Exclude values &gt;168 hours from analysis.</t>
-  </si>
-  <si>
-    <t>Instruction metadata extraction from REDCap DD</t>
-  </si>
-  <si>
-    <t>Instruction</t>
-  </si>
-  <si>
-    <t>Instruction text in each form's metadata is automatically extracted from the most recent `instruction` field in the REDCap Data Dictionary (based on field order). Because this process is automated, it may produce the following issues: (1) If an instruction spans multiple fields, only the last portion will be captured and/or (2) Some fields may display text intended for a previous section. Until this is corrected, please refer to original forms for accurate instruction text.</t>
-  </si>
-  <si>
-    <t>BIDs run label not in chronological order</t>
-  </si>
-  <si>
-    <t>Cecile Madjar</t>
-  </si>
-  <si>
-    <t>Run ID</t>
-  </si>
-  <si>
-    <t>The `run-{X}` field may not reflect chronological acquisition order. While this affects both **raw BIDS and derivatives**, data remain internally consistent (i.e. run IDs match between raw and processed datasets).</t>
-  </si>
-  <si>
-    <t>BISQR: infant sleep score - need to add</t>
-  </si>
-  <si>
-    <t>BISQ-SF</t>
-  </si>
-  <si>
-    <t>Add Infant Sleep (IS) sub-scale score to `ph_cg_bisq`.</t>
-  </si>
-  <si>
-    <t>pex_bm_healthv2_preg__exp__pnv_007__01 is completely blank</t>
-  </si>
-  <si>
-    <t>Stephanie Averill</t>
-  </si>
-  <si>
-    <t>Ongoing</t>
-  </si>
-  <si>
-    <t>Healthv2 Preg</t>
-  </si>
-  <si>
-    <t>The field for the date when PNV was stopped (`pex_bm_healthv2_preg__exp__pnv_007__01`) is blank, despite participants having reported stopping.</t>
-  </si>
-  <si>
-    <t>aspirin items in health v2 preg</t>
-  </si>
-  <si>
-    <t>Note that items about aspirin use (`pex_bm_healthv2_preg__exp__pnv_{011|012}`) are largely blank.</t>
-  </si>
-  <si>
-    <t>MRI Derivatives - QSIprep - Generate tabular data for QSIRECON</t>
-  </si>
-  <si>
-    <t>QSIRecon</t>
-  </si>
-  <si>
-    <t>Tabulated data for QSIRecon (participant data combined across derivative files into single tidy table) will be provided in a future release.</t>
-  </si>
-  <si>
-    <t>DD 'instruction' field all blank</t>
-  </si>
-  <si>
-    <t>The 'instruction' data dictionary element is currently blank.</t>
-  </si>
-  <si>
-    <t>8 PNR not administered V1 portion of TLFB</t>
-  </si>
-  <si>
-    <t>Stephanie Averill, Santiago Torres Gomez</t>
-  </si>
-  <si>
-    <t>Select participants (N=8) were recruited postnatally, but not administered the V1 portion of the TLFB. When this was recognized, the participants were administered the TLFB at the next in-person visit, resulting in a longer recall period than specified in the protocol.</t>
-  </si>
-  <si>
-    <t>Early Child Care and Education</t>
-  </si>
-  <si>
-    <t>ECHO</t>
-  </si>
-  <si>
-    <t>Addition of the Early Child Care and Education</t>
-  </si>
-  <si>
-    <t>Addition of date to OSPREY pipeline time string</t>
-  </si>
-  <si>
-    <t>fMRI V08 video task processing pipeline</t>
-  </si>
-  <si>
-    <t>fMRI video task consistency</t>
-  </si>
-  <si>
-    <t>SSL based QALAS pipeline</t>
+    <t>A future release will include reliability codes integrated into the primary coding dataset. Until then, users must perform this integration manually: see the ERICA Data Warning for instructions. Instructions include cleaning the current files to exclude n=44 participants with incorrect code values (data entry/form errors), capping `b_raw` values at 3.0 (n=3 participants), and removing the “Locomotor Ability” field (`mh_cg_erica_3_9m_locomotor_ability`), which has errors, also to be corrected in the next release.</t>
   </si>
 </sst>
 </file>
@@ -763,7 +742,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -778,11 +757,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC4C4C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD326"/>
       </patternFill>
     </fill>
     <fill>
@@ -832,11 +806,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF563E3E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF9D50DD"/>
       </patternFill>
     </fill>
@@ -847,12 +816,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF563E3E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCAB641"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF037F4C"/>
+        <fgColor rgb="FF784BD1"/>
       </patternFill>
     </fill>
     <fill>
@@ -862,12 +836,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF784BD1"/>
+        <fgColor rgb="FFFF7575"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF7575"/>
+        <fgColor rgb="FF037F4C"/>
       </patternFill>
     </fill>
   </fills>
@@ -883,7 +857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -946,9 +920,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1290,11 +1261,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="12" width="20" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" customWidth="1"/>
+    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col min="6" max="6" width="39" customWidth="1"/>
+    <col min="7" max="7" width="5.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="29" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="31" customWidth="1"/>
+    <col min="11" max="11" width="150" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1354,13 +1334,13 @@
       <c r="F2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="3" t="s">
@@ -1369,7 +1349,7 @@
       <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1387,33 +1367,33 @@
         <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="H3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -1425,39 +1405,39 @@
         <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
       </c>
       <c r="C5" s="3">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>13</v>
@@ -1465,31 +1445,31 @@
       <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="12" t="s">
+      <c r="K5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -1501,33 +1481,33 @@
         <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -1539,39 +1519,39 @@
         <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
       </c>
       <c r="C8" s="3">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>13</v>
@@ -1579,145 +1559,145 @@
       <c r="E8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="F8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
       </c>
       <c r="C9" s="3">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="L9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3">
         <v>3</v>
       </c>
       <c r="C10" s="3">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B11" s="3">
         <v>3</v>
       </c>
       <c r="C11" s="3">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="8" t="s">
+      <c r="H11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B12" s="3">
         <v>3</v>
@@ -1729,33 +1709,33 @@
         <v>13</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="8" t="s">
+      <c r="H12" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="L12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B13" s="3">
         <v>3</v>
@@ -1767,33 +1747,33 @@
         <v>13</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="L13" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B14" s="3">
         <v>3</v>
@@ -1805,33 +1785,33 @@
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B15" s="3">
         <v>3</v>
@@ -1843,33 +1823,33 @@
         <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -1881,33 +1861,33 @@
         <v>13</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="L16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B17" s="3">
         <v>3</v>
@@ -1919,33 +1899,33 @@
         <v>13</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>82</v>
+        <v>24</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="L17" s="13" t="s">
-        <v>84</v>
+      <c r="L17" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B18" s="3">
         <v>3</v>
@@ -1957,109 +1937,109 @@
         <v>13</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" s="8" t="s">
+      <c r="H18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L18" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="L18" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3">
         <v>3</v>
       </c>
       <c r="C19" s="3">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="L19" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L19" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B20" s="3">
         <v>3</v>
       </c>
       <c r="C20" s="3">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="L20" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L20" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B21" s="3">
         <v>3</v>
@@ -2071,77 +2051,77 @@
         <v>13</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H21" s="7" t="s">
+      <c r="F21" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="L21" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L21" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B22" s="3">
         <v>3</v>
       </c>
       <c r="C22" s="3">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L22" s="8" t="s">
+      <c r="L22" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B23" s="3">
         <v>3</v>
       </c>
       <c r="C23" s="3">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>13</v>
@@ -2149,31 +2129,31 @@
       <c r="E23" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I23" s="8" t="s">
+      <c r="F23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="L23" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L23" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
@@ -2185,33 +2165,33 @@
         <v>13</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="L24" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="L24" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B25" s="3">
         <v>3</v>
@@ -2223,33 +2203,33 @@
         <v>13</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" s="8" t="s">
+      <c r="F25" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="L25" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="L25" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B26" s="3">
         <v>3</v>
@@ -2261,71 +2241,71 @@
         <v>13</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B27" s="3">
         <v>3</v>
       </c>
       <c r="C27" s="3">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>16</v>
+      <c r="F27" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>114</v>
+        <v>33</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>114</v>
+        <v>105</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B28" s="3">
         <v>3</v>
@@ -2337,71 +2317,71 @@
         <v>13</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I28" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L28" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L28" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B29" s="3">
         <v>3</v>
       </c>
       <c r="C29" s="3">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I29" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L29" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B30" s="3">
         <v>3</v>
@@ -2413,33 +2393,33 @@
         <v>13</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I30" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L30" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L30" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B31" s="3">
         <v>3</v>
@@ -2451,39 +2431,39 @@
         <v>13</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="H31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="L31" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="L31" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B32" s="3">
         <v>3</v>
       </c>
       <c r="C32" s="3">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>13</v>
@@ -2491,31 +2471,31 @@
       <c r="E32" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="12" t="s">
-        <v>34</v>
+      <c r="F32" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="L32" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="L32" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B33" s="3">
         <v>3</v>
@@ -2527,33 +2507,33 @@
         <v>13</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G33" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" s="7" t="s">
+      <c r="G33" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="L33" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="L33" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B34" s="3">
         <v>3</v>
@@ -2565,71 +2545,71 @@
         <v>13</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G34" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="H34" s="7" t="s">
+      <c r="G34" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="I34" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="L34" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="L34" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B35" s="3">
         <v>3</v>
       </c>
       <c r="C35" s="3">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H35" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="L35" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="L35" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B36" s="3">
         <v>3</v>
@@ -2641,71 +2621,71 @@
         <v>13</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G36" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H36" s="7" t="s">
+      <c r="G36" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="I36" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L36" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="L36" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B37" s="3">
         <v>3</v>
       </c>
       <c r="C37" s="3">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>23</v>
+        <v>14</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H37" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="H37" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="8" t="s">
+      <c r="I37" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="L37" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="L37" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B38" s="3">
         <v>3</v>
@@ -2717,33 +2697,33 @@
         <v>13</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G38" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H38" s="7" t="s">
+      <c r="G38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I38" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="L38" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="L38" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B39" s="3">
         <v>3</v>
@@ -2755,33 +2735,33 @@
         <v>13</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G39" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="H39" s="7" t="s">
+      <c r="G39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="I39" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="L39" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="L39" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B40" s="3">
         <v>3</v>
@@ -2793,33 +2773,33 @@
         <v>13</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G40" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" s="7" t="s">
+      <c r="G40" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I40" s="8" t="s">
+      <c r="I40" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="L40" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="L40" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B41" s="3">
         <v>3</v>
@@ -2831,109 +2811,109 @@
         <v>13</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H41" s="7" t="s">
+      <c r="H41" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="I41" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="L41" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="L41" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B42" s="3">
         <v>3</v>
       </c>
       <c r="C42" s="3">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="G42" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="I42" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L42" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="L42" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B43" s="3">
         <v>3</v>
       </c>
       <c r="C43" s="3">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I43" s="8" t="s">
-        <v>18</v>
+      <c r="I43" s="19" t="s">
+        <v>154</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L43" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="L43" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B44" s="3">
         <v>3</v>
@@ -2945,109 +2925,109 @@
         <v>13</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>23</v>
+        <v>14</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I44" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I44" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="L44" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="L44" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B45" s="3">
         <v>3</v>
       </c>
       <c r="C45" s="3">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G45" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="L45" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="L45" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B46" s="3">
         <v>3</v>
       </c>
       <c r="C46" s="3">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I46" s="20" t="s">
-        <v>173</v>
+        <v>23</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="L46" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="L46" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B47" s="3">
         <v>3</v>
@@ -3064,28 +3044,28 @@
       <c r="F47" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G47" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I47" s="8" t="s">
+      <c r="G47" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I47" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="L47" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="L47" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B48" s="3">
         <v>3</v>
@@ -3097,33 +3077,33 @@
         <v>13</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G48" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="H48" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>179</v>
+        <v>13</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="L48" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B49" s="3">
         <v>3</v>
@@ -3135,33 +3115,33 @@
         <v>13</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H49" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I49" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="L49" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="L49" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B50" s="3">
         <v>3</v>
@@ -3173,71 +3153,71 @@
         <v>13</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G50" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H50" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>187</v>
+        <v>13</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="L50" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B51" s="3">
-        <v>3</v>
-      </c>
-      <c r="C51" s="3">
-        <v>30</v>
+        <v>178</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H51" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I51" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="L51" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="L51" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -3248,34 +3228,34 @@
       <c r="D52" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E52" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H52" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>114</v>
+      <c r="E52" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L52" s="4" t="s">
-        <v>114</v>
+        <v>183</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -3287,36 +3267,36 @@
         <v>13</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I53" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I53" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="L53" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="L53" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B54" s="3">
-        <v>3</v>
+        <v>187</v>
+      </c>
+      <c r="B54" t="s">
+        <v>13</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
@@ -3325,33 +3305,33 @@
         <v>13</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H54" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>114</v>
+        <v>23</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>13</v>
+        <v>188</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -3363,33 +3343,33 @@
         <v>13</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I55" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I55" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="L55" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="L55" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -3401,33 +3381,33 @@
         <v>13</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F56" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G56" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H56" s="7" t="s">
+      <c r="F56" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I56" s="8" t="s">
+      <c r="I56" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="L56" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="L56" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -3439,33 +3419,33 @@
         <v>13</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G57" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I57" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I57" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L57" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="L57" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -3477,33 +3457,33 @@
         <v>13</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>23</v>
+        <v>199</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>200</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I58" s="16" t="s">
-        <v>82</v>
+        <v>74</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="L58" s="4" t="s">
-        <v>114</v>
+        <v>204</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -3514,34 +3494,34 @@
       <c r="D59" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>213</v>
+      <c r="E59" t="s">
+        <v>13</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G59" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I59" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="L59" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="L59" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -3553,33 +3533,33 @@
         <v>13</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I60" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I60" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="L60" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L60" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -3591,71 +3571,71 @@
         <v>13</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="G61" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H61" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I61" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="I61" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>222</v>
+        <v>67</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="L61" s="8" t="s">
-        <v>21</v>
+        <v>212</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B62" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" t="s">
-        <v>13</v>
+        <v>213</v>
+      </c>
+      <c r="B62" s="3">
+        <v>3</v>
+      </c>
+      <c r="C62" s="3">
+        <v>30</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="G62" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I62" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L62" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="L62" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -3669,31 +3649,31 @@
       <c r="E63" t="s">
         <v>13</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G63" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I63" s="8" t="s">
-        <v>18</v>
+      <c r="F63" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>227</v>
+        <v>13</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="L63" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -3704,34 +3684,34 @@
       <c r="D64" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G64" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H64" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>18</v>
+      <c r="E64" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>210</v>
+        <v>13</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="L64" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -3742,222 +3722,184 @@
       <c r="D65" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E65" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G65" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H65" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="I65" s="8" t="s">
-        <v>18</v>
+      <c r="E65" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B66" s="3">
-        <v>3</v>
-      </c>
-      <c r="C66" s="3">
-        <v>30</v>
+        <v>221</v>
+      </c>
+      <c r="B66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I66" s="8" t="s">
-        <v>18</v>
+      <c r="E66" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="L66" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B67" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" t="s">
-        <v>13</v>
+        <v>222</v>
+      </c>
+      <c r="B67" s="3">
+        <v>3</v>
+      </c>
+      <c r="C67" s="3">
+        <v>30</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E67" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>114</v>
+      <c r="E67" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>13</v>
+        <v>225</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L67" s="4" t="s">
-        <v>114</v>
+        <v>226</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B68" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" t="s">
-        <v>13</v>
+        <v>227</v>
+      </c>
+      <c r="B68" s="3">
+        <v>3</v>
+      </c>
+      <c r="C68" s="3">
+        <v>30</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E68" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>114</v>
+      <c r="E68" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>13</v>
+        <v>227</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L68" s="4" t="s">
-        <v>114</v>
+        <v>229</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B69" t="s">
-        <v>13</v>
-      </c>
-      <c r="C69" t="s">
-        <v>13</v>
+        <v>230</v>
+      </c>
+      <c r="B69" s="3">
+        <v>3</v>
+      </c>
+      <c r="C69" s="3">
+        <v>30.1</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E69" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>114</v>
+      <c r="E69" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>13</v>
+        <v>231</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L69" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B70" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L70" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>232</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/tools/latest.xlsx
+++ b/tools/latest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10911"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E26D21-8B95-B14D-B802-7E1B2D4E0996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD37F8C5-7917-F24A-99BC-E4134BFF0826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="237">
   <si>
     <t>Name</t>
   </si>
@@ -717,13 +717,22 @@
   </si>
   <si>
     <t>A future release will include reliability codes integrated into the primary coding dataset. Until then, users must perform this integration manually: see the ERICA Data Warning for instructions. Instructions include cleaning the current files to exclude n=44 participants with incorrect code values (data entry/form errors), capping `b_raw` values at 3.0 (n=3 participants), and removing the “Locomotor Ability” field (`mh_cg_erica_3_9m_locomotor_ability`), which has errors, also to be corrected in the next release.</t>
+  </si>
+  <si>
+    <t>[DATA ISSUE] Diffusion MRI</t>
+  </si>
+  <si>
+    <t>dMRI metadata</t>
+  </si>
+  <si>
+    <t>`LargeDelta` and `SmallDelta` in the sidecars currently are set to vendor-specific values (which aren't always correct because the models have their own values) and ﻿will be updated to reflect accurate values.﻿ ﻿</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -740,6 +749,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="21">
@@ -857,7 +873,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -922,6 +938,7 @@
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1261,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.33203125" customWidth="1"/>
@@ -3709,7 +3726,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>220</v>
       </c>
@@ -3747,7 +3764,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>221</v>
       </c>
@@ -3785,7 +3802,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>222</v>
       </c>
@@ -3823,7 +3840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>227</v>
       </c>
@@ -3861,7 +3878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>230</v>
       </c>
@@ -3899,7 +3916,36 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="26.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="1:13" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>234</v>
+      </c>
+      <c r="E70" s="22"/>
+      <c r="F70" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I70" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J70" t="s">
+        <v>235</v>
+      </c>
+      <c r="K70" t="s">
+        <v>236</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
